--- a/Estrutura_04.01.3.000598.xlsx
+++ b/Estrutura_04.01.3.000598.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,6 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>04.01.3.000598</t>
@@ -505,15 +504,12 @@
           <t>VÁLVULA BORBOLETA DUPLA ALAVANCA DN 700 .</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -586,8 +582,6 @@
       <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -619,8 +613,6 @@
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -652,8 +644,6 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -685,8 +675,6 @@
       <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -718,8 +706,6 @@
       <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -751,8 +737,6 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -784,8 +768,6 @@
       <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -817,8 +799,6 @@
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -850,8 +830,6 @@
       <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -883,8 +861,6 @@
       <c r="G13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -916,8 +892,6 @@
       <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -949,8 +923,6 @@
       <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -982,8 +954,6 @@
       <c r="G16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1015,8 +985,6 @@
       <c r="G17" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1048,8 +1016,6 @@
       <c r="G18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1086,7 +1052,6 @@
           <t>ASTM A36</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1123,7 +1088,6 @@
           <t>ASTM A516 GR70</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1160,7 +1124,6 @@
           <t>AISI 304</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1197,7 +1160,6 @@
           <t>AISI 304</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1234,7 +1196,6 @@
           <t>ASTM A516 GR70</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1266,8 +1227,6 @@
       <c r="G24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1299,8 +1258,6 @@
       <c r="G25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1332,8 +1289,6 @@
       <c r="G26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1365,8 +1320,6 @@
       <c r="G27" t="n">
         <v>4</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1403,7 +1356,6 @@
           <t>ASTM A36</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1440,7 +1392,6 @@
           <t>ASTM A36</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1477,7 +1428,6 @@
           <t>SAE 1045</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1514,7 +1464,6 @@
           <t>AÇO INOX AISI 420</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1551,7 +1500,6 @@
           <t>ASTM A516 GR70</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1583,8 +1531,6 @@
       <c r="G33" t="n">
         <v>1</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1616,8 +1562,6 @@
       <c r="G34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1649,8 +1593,6 @@
       <c r="G35" t="n">
         <v>1</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1728,7 +1670,6 @@
           <t>SAE 8550</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1765,7 +1706,6 @@
           <t>SAE 8550</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1802,7 +1742,6 @@
           <t>ASTM A516 GR70</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1834,8 +1773,6 @@
       <c r="G40" t="n">
         <v>2</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1867,8 +1804,6 @@
       <c r="G41" t="n">
         <v>2</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1900,8 +1835,6 @@
       <c r="G42" t="n">
         <v>2</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1933,8 +1866,6 @@
       <c r="G43" t="n">
         <v>2</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1966,8 +1897,6 @@
       <c r="G44" t="n">
         <v>2</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2004,7 +1933,6 @@
           <t>SAE 8550</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2041,7 +1969,6 @@
           <t>ASTM A516 GR70</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2073,8 +2000,6 @@
       <c r="G47" t="n">
         <v>1</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2106,8 +2031,6 @@
       <c r="G48" t="n">
         <v>1</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2139,8 +2062,6 @@
       <c r="G49" t="n">
         <v>2</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2172,8 +2093,6 @@
       <c r="G50" t="n">
         <v>2</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2205,8 +2124,6 @@
       <c r="G51" t="n">
         <v>2</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2284,7 +2201,6 @@
           <t>SAE 8550</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2321,7 +2237,6 @@
           <t>ASTM A516 GR70</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2358,7 +2273,6 @@
           <t>ASTM A36</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2395,7 +2309,6 @@
           <t>ASTM A516 GR70</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2432,7 +2345,6 @@
           <t>ASTM A516 GR70</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2469,7 +2381,6 @@
           <t>ASTM A516 GR70</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2506,7 +2417,6 @@
           <t>SAE 8550</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2543,7 +2453,6 @@
           <t>SAE 8550</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2580,7 +2489,6 @@
           <t>SAE 8550</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2658,7 +2566,6 @@
           <t>ASTM A36</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2695,7 +2602,6 @@
           <t>ASTM A36</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2727,8 +2633,6 @@
       <c r="G65" t="n">
         <v>1</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2760,8 +2664,6 @@
       <c r="G66" t="n">
         <v>1</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2793,8 +2695,6 @@
       <c r="G67" t="n">
         <v>2</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2826,8 +2726,6 @@
       <c r="G68" t="n">
         <v>1</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2840,50 +2738,58 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>03.04.01.3.000598-19-REC</t>
+          <t>03.022-007347-REC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BUCHA ESTRIADA</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>CONJUNTO DISCO USINADO</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>022-007347</t>
+        </is>
+      </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Existe no Nomus mas NÃO tem desenho neste PDF — confirmar.</t>
+          <t>Disco existente (REC) 022-007348.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007347-REC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>03.022-007347-REC</t>
+          <t>03.022-007346-1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CONJUNTO DISCO USINADO</t>
+          <t>CONJUNTO DISCO SOLDADO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>022-007347</t>
+          <t>022-007346</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2891,40 +2797,30 @@
       </c>
       <c r="G70" t="n">
         <v>1</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Disco existente (REC) 022-007348.</t>
-        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>03.022-007347-REC</t>
+          <t>03.022-007346-1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>03.022-007346-1</t>
+          <t>03.022-007349</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CONJUNTO DISCO SOLDADO</t>
+          <t>BASE DO DISCO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>022-007346</t>
+          <t>022-007349</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2933,72 +2829,12 @@
       <c r="G71" t="n">
         <v>1</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>3</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>03.022-007346-1</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>03.022-007349</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BASE DO DISCO</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>022-007349</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="72"/>
     <row r="73">
-      <c r="A73" t="n">
-        <v>1</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>03.04.01.3.000598-21-REC</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>TAMPA JANELA DE INSPEÇÃO</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Existe no Nomus mas NÃO tem desenho neste PDF — confirmar.</t>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>COMPRADOS / NORMALIZADOS (sem código no PDF do Nomus)</t>
         </is>
       </c>
     </row>
@@ -3011,27 +2847,22 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>03.04.01.3.000598-22-REC</t>
-        </is>
-      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ATUADOR</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>ROLAM. AUTO-COMPENS. DE ROLOS</t>
+        </is>
+      </c>
       <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>SKF 22312 E Ø60 x Ø130 x 46mm</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Existe no Nomus mas NÃO tem desenho neste PDF — confirmar.</t>
+          <t>Código Nomus a informar</t>
         </is>
       </c>
     </row>
@@ -3044,36 +2875,78 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>03.04.01.3.000598-23-REC</t>
-        </is>
-      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CHAVETA MENOR</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>ANEL ELÁSTICO</t>
+        </is>
+      </c>
       <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>SAE 1070 Ø60 x 2 DIN 471</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Existe no Nomus mas NÃO tem desenho neste PDF — confirmar.</t>
+          <t>Código Nomus a informar</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GAXETA QUAD. 2202 TEADIT</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>10</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>CARBONO + GRAFITE 3/8" x 3/8" x 3000MM</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Código Nomus a informar</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>COMPRADOS / NORMALIZADOS (sem código no PDF do Nomus)</t>
+      <c r="A77" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>PINO ROSCADO M12 x 60</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>4</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>CL. 8.8 DIN 976 ZINCADO</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Código Nomus a informar</t>
         </is>
       </c>
     </row>
@@ -3086,20 +2959,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ROLAM. AUTO-COMPENS. DE ROLOS</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>ARRUELA LISA A-13</t>
+        </is>
+      </c>
       <c r="F78" t="n">
-        <v>2</v>
-      </c>
-      <c r="G78" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SKF 22312 E Ø60 x Ø130 x 46mm</t>
+          <t>CL. 8.8 DIN 125 ZINCADO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3117,20 +2987,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ANEL ELÁSTICO</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>PORCA SEXTAVADA M12</t>
+        </is>
+      </c>
       <c r="F79" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SAE 1070 Ø60 x 2 DIN 471</t>
+          <t>CL. 8.8 DIN 934 ZINCADO</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3148,20 +3015,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>GAXETA QUAD. 2202 TEADIT</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>PARAF. CAB. SEXTAVADA M30 x 100</t>
+        </is>
+      </c>
       <c r="F80" t="n">
-        <v>10</v>
-      </c>
-      <c r="G80" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CARBONO + GRAFITE 3/8" x 3/8" x 3000MM</t>
+          <t>Gr. 8.8 DIN 933</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3179,20 +3043,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PINO ROSCADO M12 x 60</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>ARRUELA DE PRESSÃO A-31</t>
+        </is>
+      </c>
       <c r="F81" t="n">
-        <v>4</v>
-      </c>
-      <c r="G81" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CL. 8.8 DIN 976 ZINCADO</t>
+          <t>DIN 127</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3210,20 +3071,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ARRUELA LISA A-13</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>PORCA SEXTAVADA M30</t>
+        </is>
+      </c>
       <c r="F82" t="n">
-        <v>10</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CL. 8.8 DIN 125 ZINCADO</t>
+          <t>Gr.8 DIN 934</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3241,20 +3099,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M12</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>PARAF. CAB. SEXTAVADA M16 x 50</t>
+        </is>
+      </c>
       <c r="F83" t="n">
-        <v>4</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CL. 8.8 DIN 934 ZINCADO</t>
+          <t>Gr. 8.8 DIN 933</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3272,20 +3127,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M30 x 100</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>PORCA SEXTAVADA M16</t>
+        </is>
+      </c>
       <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
+        <v>17</v>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Gr. 8.8 DIN 933</t>
+          <t>Gr.8 DIN 934</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3303,20 +3155,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ARRUELA DE PRESSÃO A-31</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>ANEL O'RING</t>
+        </is>
+      </c>
       <c r="F85" t="n">
-        <v>2</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>DIN 127</t>
+          <t>VITON FKM 70-75 Sh-A Ø641 x Ø10mm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3334,20 +3183,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M30</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>PARAF.ALLEN S/ CAB. SEXT. INTERNO M6 x 25</t>
+        </is>
+      </c>
       <c r="F86" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Gr.8 DIN 934</t>
+          <t>Gr. 8.8 DIN 913</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3365,20 +3211,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M16 x 50</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>PORCA SEXTAVADA M6</t>
+        </is>
+      </c>
       <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Gr. 8.8 DIN 933</t>
+          <t>Gr.8 DIN 934</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3396,17 +3239,14 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M16</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>PORCA SEXTAVADA M10</t>
+        </is>
+      </c>
       <c r="F88" t="n">
-        <v>17</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
+        <v>8</v>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Gr.8 DIN 934</t>
@@ -3427,20 +3267,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ANEL O'RING</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>PARAF.ALLEN S/ CAB. SEXT. INTERNO M10 x 40</t>
+        </is>
+      </c>
       <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>VITON FKM 70-75 Sh-A Ø641 x Ø10mm</t>
+          <t>Gr. 8.8 DIN 913</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -3458,20 +3295,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PARAF.ALLEN S/ CAB. SEXT. INTERNO M6 x 25</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>ARRUELA LISA A-10,5</t>
+        </is>
+      </c>
       <c r="F90" t="n">
-        <v>6</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
+        <v>28</v>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Gr. 8.8 DIN 913</t>
+          <t>CL. 8.8 DIN 125</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -3489,20 +3323,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M6</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>PARAF. CAB. SEXTAVADA M10 x 45</t>
+        </is>
+      </c>
       <c r="F91" t="n">
         <v>6</v>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Gr.8 DIN 934</t>
+          <t>Gr. 8.8 DIN 933</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -3520,20 +3351,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M10</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>PARAF. CAB. SEXTAVADA M12 x 30</t>
+        </is>
+      </c>
       <c r="F92" t="n">
-        <v>8</v>
-      </c>
-      <c r="G92" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Gr.8 DIN 934</t>
+          <t>Gr. 8.8 DIN 933</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -3551,20 +3379,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PARAF.ALLEN S/ CAB. SEXT. INTERNO M10 x 40</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>PARAF. CAB. SEXTAVADA M8 x 30</t>
+        </is>
+      </c>
       <c r="F93" t="n">
-        <v>2</v>
-      </c>
-      <c r="G93" t="inlineStr"/>
+        <v>8</v>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Gr. 8.8 DIN 913</t>
+          <t>Gr. 8.8 DIN 933</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -3582,20 +3407,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ARRUELA LISA A-10,5</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>PARAF. CAB. SEXTAVADA M10 x 25</t>
+        </is>
+      </c>
       <c r="F94" t="n">
-        <v>28</v>
-      </c>
-      <c r="G94" t="inlineStr"/>
+        <v>8</v>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>CL. 8.8 DIN 125</t>
+          <t>Gr. 8.8 DIN 933</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -3613,17 +3435,14 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M10 x 45</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>PARAF. CAB. SEXTAVADA M16 x 45</t>
+        </is>
+      </c>
       <c r="F95" t="n">
-        <v>6</v>
-      </c>
-      <c r="G95" t="inlineStr"/>
+        <v>8</v>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Gr. 8.8 DIN 933</t>
@@ -3644,17 +3463,14 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M12 x 30</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>PARAF. CAB. SEXTAVADA M16 x 65</t>
+        </is>
+      </c>
       <c r="F96" t="n">
-        <v>6</v>
-      </c>
-      <c r="G96" t="inlineStr"/>
+        <v>16</v>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Gr. 8.8 DIN 933</t>
@@ -3675,20 +3491,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M8 x 30</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+          <t>NIPLE</t>
+        </is>
+      </c>
       <c r="F97" t="n">
-        <v>8</v>
-      </c>
-      <c r="G97" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Gr. 8.8 DIN 933</t>
+          <t>AISI 304 1/4" NPT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -3706,20 +3519,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M10 x 25</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>TAMPÃO Ø1" ROSCA BSP ANSI B16.3</t>
+        </is>
+      </c>
       <c r="F98" t="n">
-        <v>8</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Gr. 8.8 DIN 933</t>
+          <t>ASTM A 197</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -3737,20 +3547,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M16 x 45</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>UNIÃO ORIENTÁVEL SIMPLES</t>
+        </is>
+      </c>
       <c r="F99" t="n">
-        <v>8</v>
-      </c>
-      <c r="G99" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Gr. 8.8 DIN 933</t>
+          <t>AISI 304 1/4" NPT</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -3768,20 +3575,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M16 x 65</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>DISTRIBUIDOR LINHA DUPLA BM-4</t>
+        </is>
+      </c>
       <c r="F100" t="n">
-        <v>16</v>
-      </c>
-      <c r="G100" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Gr. 8.8 DIN 933</t>
+          <t>04 MÓDULOS/08 SAÍDAS EXIMPORT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -3799,20 +3603,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NIPLE</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
+          <t>ARRUELA LISA A-8,1</t>
+        </is>
+      </c>
       <c r="F101" t="n">
-        <v>10</v>
-      </c>
-      <c r="G101" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>AISI 304 1/4" NPT</t>
+          <t>CL. 8.8 DIN 125</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -3830,20 +3631,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TAMPÃO Ø1" ROSCA BSP ANSI B16.3</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>PORCA SEXTAVADA M10</t>
+        </is>
+      </c>
       <c r="F102" t="n">
         <v>2</v>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ASTM A 197</t>
+          <t>Gr.8 DIN 934</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -3861,17 +3659,14 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>UNIÃO ORIENTÁVEL SIMPLES</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>TÊ ROSCA FÊMEA 6000Lbs</t>
+        </is>
+      </c>
       <c r="F103" t="n">
-        <v>2</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>AISI 304 1/4" NPT</t>
@@ -3892,20 +3687,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DISTRIBUIDOR LINHA DUPLA BM-4</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>TUBO Ø10 PAREDE 1MM X 6000MM</t>
+        </is>
+      </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>04 MÓDULOS/08 SAÍDAS EXIMPORT</t>
+          <t>AISI 304</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -3923,20 +3715,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ARRUELA LISA A-8,1</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>CONEXÃO JOELHO PARA TUBO 10MM</t>
+        </is>
+      </c>
       <c r="F105" t="n">
         <v>2</v>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>CL. 8.8 DIN 125</t>
+          <t>AISI 304 1/4" NPT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -3954,20 +3743,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M10</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>PARAF.ALLEN C/CAB.SEXT. INTER. M6 x 55</t>
+        </is>
+      </c>
       <c r="F106" t="n">
         <v>2</v>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Gr.8 DIN 934</t>
+          <t>Gr. 8.8 DIN 912</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -3985,20 +3771,17 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>TÊ ROSCA FÊMEA 6000Lbs</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>GAXETA QUAD. 2202 TEADIT</t>
+        </is>
+      </c>
       <c r="F107" t="n">
-        <v>4</v>
-      </c>
-      <c r="G107" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>AISI 304 1/4" NPT</t>
+          <t>CARBONO + GRAFITE 1/4" x 1/4" x 900MM</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4016,25 +3799,27 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>TUBO Ø10 PAREDE 1MM X 6000MM</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>JUNTA METALBEST (022-007370)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>022-007370</t>
+        </is>
+      </c>
       <c r="F108" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>AISI 304</t>
+          <t>INOX / GRAFITE</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Comprado — código Nomus a informar</t>
         </is>
       </c>
     </row>
@@ -4047,145 +3832,12 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CONEXÃO JOELHO PARA TUBO 10MM</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="n">
-        <v>2</v>
-      </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>AISI 304 1/4" NPT</t>
+          <t>PENDENTE: balões 52, 62, 65 sem linha na lista do desenho</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
-        <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>1</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>PARAF.ALLEN C/CAB.SEXT. INTER. M6 x 55</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="n">
-        <v>2</v>
-      </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 912</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>1</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>GAXETA QUAD. 2202 TEADIT</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>CARBONO + GRAFITE 1/4" x 1/4" x 900MM</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>JUNTA METALBEST (022-007370)</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>022-007370</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>2</v>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>INOX / GRAFITE</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Comprado — código Nomus a informar</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>1</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>PENDENTE: balões 52, 62, 65 sem linha na lista do desenho</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
         <is>
           <t>Definir descrição, material e qtd</t>
         </is>

--- a/Estrutura_04.01.3.000598.xlsx
+++ b/Estrutura_04.01.3.000598.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estrutura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A conferir" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,18 +430,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:J161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,32 +463,37 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Descrição</t>
+          <t>Descrição (Nomus)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Un</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Nº desenho</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Qtd por pai</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Qtd total OS</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Material (desenho da peça)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Observação</t>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Observação / conferir</t>
         </is>
       </c>
     </row>
@@ -504,12 +511,23 @@
           <t>VÁLVULA BORBOLETA DUPLA ALAVANCA DN 700 .</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Produto acabado</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -532,21 +550,26 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>022-007303</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
+      <c r="H3" t="n">
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Corpo existente (REC).</t>
         </is>
@@ -573,15 +596,26 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>022-007302</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -604,45 +638,65 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>022-007307</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03.022-007302-1</t>
+          <t>03.022-007307</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>03.022-007308</t>
+          <t>01.13.1.57.14.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FLANGE</t>
+          <t>TUBO Ø175 x Ø150 ASTM A516 Gr 70 .</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>022-007308</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>125</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -656,55 +710,75 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>03.022-007304</t>
+          <t>03.022-007308</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BOSSE 1</t>
+          <t>FLANGE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>022-007304</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>022-007308</t>
+        </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>03.022-007302-1</t>
+          <t>03.022-007308</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>03.022-007305</t>
+          <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BOSSE 2</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>022-007305</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>6.2</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -718,25 +792,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03.022-007312</t>
+          <t>03.022-007304</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CONJUNTO SUPORTE USINADO</t>
+          <t>BOSSE 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>022-007312</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>022-007304</t>
+        </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -744,91 +829,120 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>03.022-007312</t>
+          <t>03.022-007304</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03.022-007309</t>
+          <t>01.09.1.1.36.1.78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CONJUNTO SUPORTE SOLDADO</t>
+          <t>BARRA REDONDA 5" AÇO CARBONO ASTM A516 Gr.70</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>022-007309</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>125</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>03.022-007309</t>
+          <t>03.022-007302-1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>03.022-007310</t>
+          <t>03.022-007305</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CHAPA INFERIOR</t>
+          <t>BOSSE 2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>022-007310</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>022-007305</t>
+        </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>03.022-007309</t>
+          <t>03.022-007305</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>03.022-007311</t>
+          <t>01.09.1.1.12.1.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CHAPA LATERAL</t>
+          <t>BARRA REDONDA 1 1/4" AÇO CARBONO ASTM A516 Gr.70</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>022-007311</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>55</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -842,25 +956,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>03.022-007306</t>
+          <t>03.022-007312</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CONJUNTO CAVALETE SOLDADO</t>
+          <t>CONJUNTO SUPORTE USINADO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>022-007306</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>022-007312</t>
+        </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -868,528 +993,655 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>03.022-007306</t>
+          <t>03.022-007312</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>03.022-007313</t>
+          <t>03.022-007309</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PLACA DO CAVALETE</t>
+          <t>CONJUNTO SUPORTE SOLDADO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>022-007313</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>022-007309</t>
+        </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>03.022-007306</t>
+          <t>03.022-007309</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>03.022-007314</t>
+          <t>03.022-007310</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CHAPA 1</t>
+          <t>CHAPA INFERIOR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>022-007314</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>022-007310</t>
+        </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>03.022-007306</t>
+          <t>03.022-007310</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>03.022-007315</t>
+          <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CHAPA 2</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>022-007315</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.05</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>03.022-007306</t>
+          <t>03.022-007309</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>03.022-007316</t>
+          <t>03.022-007311</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NERVURA 1</t>
+          <t>CHAPA LATERAL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>022-007316</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>022-007311</t>
+        </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>03.022-007306</t>
+          <t>03.022-007311</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>03.022-007317</t>
+          <t>01.09.3.1.2.4.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NERVURA 2</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 3/4"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>022-007317</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>1.88</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007302-1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>03.022-007355</t>
+          <t>03.022-007306</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SUPORTE DO DISTRIBUIDOR</t>
+          <t>CONJUNTO CAVALETE SOLDADO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>022-007355</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>022-007306</t>
+        </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>ASTM A36</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007306</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>03.022-007326</t>
+          <t>03.022-007313</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ANEL GUARDA PÓ</t>
+          <t>PLACA DO CAVALETE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>022-007326</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>022-007313</t>
+        </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007313</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>03.022-007328</t>
+          <t>01.09.3.1.1.5.52</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ANEL LANTERNA</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>022-007328</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>AISI 304</t>
+        <v>12.46</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007306</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>03.022-007327</t>
+          <t>03.022-007314</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ANEL ANTI EXTRUSÃO</t>
+          <t>CHAPA 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>022-007327</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>022-007314</t>
+        </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>AISI 304</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007314</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>03.022-007368</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CONJUNTO JANELA DE VISITA USINADA</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>022-007368</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
+        <v>3.07</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03.022-007368</t>
+          <t>03.022-007306</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>03.022-007369</t>
+          <t>03.022-007315</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CONJUNTO JANELA DE VISITA SOLDADA</t>
+          <t>CHAPA 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>022-007369</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>022-007315</t>
+        </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03.022-007369</t>
+          <t>03.022-007315</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>03.022-007365</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FLANGE DA TAMPA</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>022-007365</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>5.88</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03.022-007369</t>
+          <t>03.022-007306</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>03.022-007367</t>
+          <t>03.022-007316</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TUBO DA TAMPA</t>
+          <t>NERVURA 1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>022-007367</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>022-007316</t>
+        </is>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03.022-007369</t>
+          <t>03.022-007316</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>03.022-007366</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NERVURA DA TAMPA</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>022-007366</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>0.59</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007306</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>03.022-007329</t>
+          <t>03.022-007317</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PREME GAXETA</t>
+          <t>NERVURA 2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>022-007329</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>022-007317</t>
+        </is>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>ASTM A36</t>
-        </is>
-      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007317</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>03.022-007330</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PRENSA GAXETA</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>022-007330</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>2</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>ASTM A36</t>
+        <v>1.54</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
@@ -1404,64 +1656,74 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>03.022-007334</t>
+          <t>03.022-007355</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CHAVETA CENTRAL</t>
+          <t>SUPORTE DO DISTRIBUIDOR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>022-007334</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>022-007355</t>
+        </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>SAE 1045</t>
-        </is>
-      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007355</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>03.022-007318</t>
+          <t>01.09.3.1.1.5.19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EIXO PRINCIPAL</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/8"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>022-007318</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>AÇO INOX AISI 420</t>
+        <v>0.86</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
@@ -1476,30 +1738,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>03.022-007333</t>
+          <t>03.022-007326</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CONJUNTO PLACA CENTRAL USINADO</t>
+          <t>ANEL GUARDA PÓ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>022-007333</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>022-007326</t>
+        </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1507,167 +1775,201 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>03.022-007333</t>
+          <t>03.022-007326</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>03.022-007331</t>
+          <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PLACA CENTRAL SOLDADA</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>022-007331</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>1.09</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>03.022-007331</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>03.022-007340</t>
+          <t>03.022-007328</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PLACA CENTRAL</t>
+          <t>ANEL LANTERNA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>022-007340</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>022-007328</t>
+        </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>03.022-007331</t>
+          <t>03.022-007328</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>03.022-007332</t>
+          <t>01.09.1.1.30.3.1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BUCHA DA PLACA CENTRAL</t>
+          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>022-007332</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>03.022-007331</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>03.022-007371</t>
+          <t>03.022-007327</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TAMPÃO</t>
+          <t>ANEL ANTI EXTRUSÃO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>022-007371</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>022-007327</t>
+        </is>
       </c>
       <c r="G36" t="n">
         <v>2</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>SAE 1020</t>
-        </is>
+      <c r="H36" t="n">
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>03.022-007331</t>
+          <t>03.022-007327</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>03.022-007336</t>
+          <t>01.09.1.1.30.3.1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BUCHA CENTRAL 2</t>
+          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>022-007336</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>SAE 8550</t>
+        <v>15</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
@@ -1682,127 +1984,159 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>03.022-007335</t>
+          <t>03.022-007368</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BUCHA CENTRAL</t>
+          <t>CONJUNTO JANELA DE VISITA USINADA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>022-007335</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>022-007368</t>
+        </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>SAE 8550</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007368</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>03.022-007342</t>
+          <t>03.022-007369</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CONJUNTO ALAVANCA USINADA</t>
+          <t>CONJUNTO JANELA DE VISITA SOLDADA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>022-007342</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>022-007369</t>
+        </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>03.022-007342</t>
+          <t>03.022-007369</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>03.022-007341</t>
+          <t>03.022-007365</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CONJUNTO ALAVANCA SOLDADA</t>
+          <t>FLANGE DA TAMPA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>022-007341</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>022-007365</t>
+        </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>03.022-007341</t>
+          <t>03.022-007365</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>03.022-007344</t>
+          <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TUBO DA ALAVANCA</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>022-007344</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>15.08</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1811,60 +2145,80 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>03.022-007341</t>
+          <t>03.022-007369</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>03.022-007343</t>
+          <t>03.022-007367</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CHAPA DA ALAVANCA</t>
+          <t>TUBO DA TAMPA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>022-007343</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>022-007367</t>
+        </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>03.022-007341</t>
+          <t>03.022-007367</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>03.022-007345</t>
+          <t>01.13.1.5.4.4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BARRA SUPERIOR DA ALAVANCA</t>
+          <t>TUBO 1" ASTM A36 SCH 80</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>022-007345</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1873,64 +2227,79 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>03.022-007341</t>
+          <t>03.022-007369</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>03.022-007350</t>
+          <t>03.022-007366</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BARRA INFERIOR DA ALAVANCA</t>
+          <t>NERVURA DA TAMPA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>022-007350</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>022-007366</t>
+        </is>
       </c>
       <c r="G44" t="n">
         <v>2</v>
       </c>
+      <c r="H44" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007366</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>03.022-007351</t>
+          <t>01.09.3.1.1.5.11</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BUCHA DO CONJUNTO ALAVANCA</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/2"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>022-007351</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>2</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>SAE 8550</t>
+        <v>0.59</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
@@ -1945,30 +2314,36 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>03.022-007352</t>
+          <t>03.022-007329</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CONJUNTO SUPORTE DO DISCO USINADO</t>
+          <t>PREME GAXETA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>022-007352</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>022-007329</t>
+        </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1976,229 +2351,283 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>03.022-007352</t>
+          <t>03.022-007329</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>03.022-007337</t>
+          <t>01.09.3.1.1.5.4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CONJUNTO SUPORTE DO DISCO SOLDADO</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>022-007337</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>03.022-007337</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>03.022-007338</t>
+          <t>03.022-007330</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BASE DO SUPORTE</t>
+          <t>PRENSA GAXETA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>022-007338</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>022-007330</t>
+        </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>03.022-007337</t>
+          <t>03.022-007330</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>03.022-007339</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CHAPA DO SUPORTE</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>022-007339</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>2</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1.72</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>03.022-007337</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>03.022-007353</t>
+          <t>03.022-007334</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BUCHA MAIOR DO SUPORTE</t>
+          <t>CHAVETA CENTRAL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>022-007353</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>022-007334</t>
+        </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>03.022-007337</t>
+          <t>03.022-007334</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>03.022-007354</t>
+          <t>01.09.1.10.224.1.22</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BUCHA MENOR DO SUPORTE</t>
+          <t>BARRA CHAVETA 17 x 25 AÇO CARBONO SAE 1045</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>022-007354</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>2</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>155</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>03.022-007337</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>03.022-007371</t>
+          <t>03.022-007318</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TAMPÃO</t>
+          <t>EIXO PRINCIPAL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>022-007371</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>022-007318</t>
+        </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>SAE 1020</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007318</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>03.022-007357</t>
+          <t>01.09.1.1.27.3.7</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BUCHA DO BRAÇO ARTICULADO</t>
+          <t>BARRA REDONDA 3" AÇO INOX AISI 420</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>022-007357</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>4</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>4</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>SAE 8550</t>
+        <v>1250</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
@@ -2213,357 +2642,408 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>03.022-007356</t>
+          <t>03.022-007333</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BRAÇO ARTICULADO</t>
+          <t>CONJUNTO PLACA CENTRAL USINADO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>022-007356</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>022-007333</t>
+        </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007333</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>03.022-007319</t>
+          <t>03.022-007331</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MANCAL</t>
+          <t>PLACA CENTRAL SOLDADA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>022-007319</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>022-007331</t>
+        </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>ASTM A36</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007331</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>03.022-007361</t>
+          <t>03.022-007340</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ANEL DE AJUSTE MAIOR</t>
+          <t>PLACA CENTRAL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>022-007361</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>022-007340</t>
+        </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007340</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>03.022-007364</t>
+          <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ANEL DE AJUSTE DO EIXO</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>022-007364</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>2</v>
-      </c>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
+        <v>11.95</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007331</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>03.022-007360</t>
+          <t>03.022-007332</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ANEL DE AJUSTE MENOR</t>
+          <t>BUCHA DA PLACA CENTRAL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>022-007360</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>4</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>022-007332</t>
+        </is>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007332</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>03.022-007358</t>
+          <t>01.13.1.58.12.24</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PINO MAIOR</t>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>022-007358</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>SAE 8550</t>
+        <v>38</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007331</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>03.022-007363</t>
+          <t>03.022-007371</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PINO MENOR DO BRAÇO</t>
+          <t>TAMPÃO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>022-007363</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>022-007371</t>
+        </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>SAE 8550</t>
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007371</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>03.022-007359</t>
+          <t>01.09.1.1.1.1.9</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PINO MENOR</t>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>022-007359</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>SAE 8550</t>
+        <v>10</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007331</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>03.022-007371</t>
+          <t>03.022-007336</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TAMPÃO</t>
+          <t>BUCHA CENTRAL 2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>022-007371</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>8</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>022-007336</t>
+        </is>
       </c>
       <c r="G62" t="n">
-        <v>8</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>SAE 1020</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007336</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>03.022-007325</t>
+          <t>01.13.1.59.12.24</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TAMPA LATERAL</t>
+          <t>TUBO Ø110 x Ø90 SAE 8550 .</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>022-007325</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>2</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>ASTM A36</t>
+        <v>30</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
@@ -2578,30 +3058,36 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>03.022-007320</t>
+          <t>03.022-007335</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SUPORTE DO ATUADOR USINADO</t>
+          <t>BUCHA CENTRAL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>022-007320</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>022-007335</t>
+        </is>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>ASTM A36</t>
-        </is>
-      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2609,92 +3095,123 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>03.022-007320</t>
+          <t>03.022-007335</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>03.022-007321</t>
+          <t>01.13.1.60.12.24</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SUPORTE DO ATUADOR SOLDADO</t>
+          <t>TUBO Ø105 x Ø60 SAE 8550 .</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>022-007321</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>03.022-007321</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>03.022-007324</t>
+          <t>03.022-007342</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CHAPA DE CONTATO DA VÁLVULA</t>
+          <t>CONJUNTO ALAVANCA USINADA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>022-007324</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>022-007342</t>
+        </is>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>03.022-007321</t>
+          <t>03.022-007342</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>03.022-007322</t>
+          <t>03.022-007341</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BASE DE LIGAÇÃO</t>
+          <t>CONJUNTO ALAVANCA SOLDADA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>022-007322</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>2</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>022-007341</t>
+        </is>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2702,167 +3219,285 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>03.022-007321</t>
+          <t>03.022-007341</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>03.022-007323</t>
+          <t>03.022-007344</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CHAPA DE CONTROLE DO ATUADOR</t>
+          <t>TUBO DA ALAVANCA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>022-007323</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>022-007344</t>
+        </is>
       </c>
       <c r="G68" t="n">
         <v>1</v>
       </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007344</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>03.022-007347-REC</t>
+          <t>01.13.1.61.1.24</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CONJUNTO DISCO USINADO</t>
+          <t>TUBO Ø4" x Ø60 ASTM A106 GR C .</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>022-007347</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>ASTM A516 GR70</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Disco existente (REC) 022-007348.</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>03.022-007347-REC</t>
+          <t>03.022-007341</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>03.022-007346-1</t>
+          <t>03.022-007343</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CONJUNTO DISCO SOLDADO</t>
+          <t>CHAPA DA ALAVANCA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>022-007346</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>022-007343</t>
+        </is>
       </c>
       <c r="G70" t="n">
         <v>1</v>
       </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
+        <v>4</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>03.022-007343</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
         <v>3</v>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>03.022-007346-1</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>03.022-007349</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>BASE DO DISCO</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>022-007349</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>03.022-007341</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>03.022-007345</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BARRA SUPERIOR DA ALAVANCA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>022-007345</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+    </row>
     <row r="73">
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>COMPRADOS / NORMALIZADOS (sem código no PDF do Nomus)</t>
-        </is>
-      </c>
+      <c r="A73" t="n">
+        <v>3</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>03.022-007341</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>03.022-007350</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BARRA INFERIOR DA ALAVANCA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>022-007350</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007350</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ROLAM. AUTO-COMPENS. DE ROLOS</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>2</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>SKF 22312 E Ø60 x Ø130 x 46mm</t>
-        </is>
-      </c>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
@@ -2875,50 +3510,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>03.022-007351</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ANEL ELÁSTICO</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>2</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>SAE 1070 Ø60 x 2 DIN 471</t>
-        </is>
+          <t>BUCHA DO CONJUNTO ALAVANCA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>022-007351</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007351</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>01.13.1.62.12.24</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>GAXETA QUAD. 2202 TEADIT</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>10</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>CARBONO + GRAFITE 3/8" x 3/8" x 3000MM</t>
-        </is>
-      </c>
+          <t>TUBO Ø35 x Ø55 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>20</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
@@ -2931,330 +3592,492 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>03.022-007352</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PINO ROSCADO M12 x 60</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>4</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>CL. 8.8 DIN 976 ZINCADO</t>
-        </is>
+          <t>CONJUNTO SUPORTE DO DISCO USINADO</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>022-007352</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007352</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>03.022-007337</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ARRUELA LISA A-13</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>10</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>CL. 8.8 DIN 125 ZINCADO</t>
-        </is>
+          <t>CONJUNTO SUPORTE DO DISCO SOLDADO</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>022-007337</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>03.022-007338</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M12</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>4</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>CL. 8.8 DIN 934 ZINCADO</t>
-        </is>
+          <t>BASE DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>022-007338</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007338</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M30 x 100</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 933</t>
-        </is>
-      </c>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>03.022-007339</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ARRUELA DE PRESSÃO A-31</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>2</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>DIN 127</t>
-        </is>
+          <t>CHAPA DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>022-007339</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007339</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M30</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Gr.8 DIN 934</t>
-        </is>
-      </c>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>03.022-007353</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M16 x 50</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 933</t>
-        </is>
+          <t>BUCHA MAIOR DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>022-007353</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007353</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>01.13.1.63.12.24</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M16</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>17</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Gr.8 DIN 934</t>
-        </is>
-      </c>
+          <t>TUBO Ø60 x Ø30 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="n">
+        <v>25</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>03.022-007354</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ANEL O'RING</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>VITON FKM 70-75 Sh-A Ø641 x Ø10mm</t>
-        </is>
+          <t>BUCHA MENOR DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>022-007354</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007354</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>01.13.1.58.12.24</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PARAF.ALLEN S/ CAB. SEXT. INTERNO M6 x 25</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>6</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 913</t>
-        </is>
-      </c>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="n">
+        <v>25</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M6</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>6</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Gr.8 DIN 934</t>
-        </is>
+          <t>TAMPÃO</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>022-007371</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>01.09.1.1.1.1.9</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M10</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>8</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Gr.8 DIN 934</t>
-        </is>
-      </c>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="n">
+        <v>10</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
         </is>
       </c>
     </row>
@@ -3267,50 +4090,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>03.022-007357</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PARAF.ALLEN S/ CAB. SEXT. INTERNO M10 x 40</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>2</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 913</t>
-        </is>
+          <t>BUCHA DO BRAÇO ARTICULADO</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>022-007357</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>4</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007357</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>01.13.1.58.12.24</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ARRUELA LISA A-10,5</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>28</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>CL. 8.8 DIN 125</t>
-        </is>
-      </c>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="n">
+        <v>20</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
@@ -3323,50 +4172,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>03.022-007356</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M10 x 45</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>6</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 933</t>
-        </is>
+          <t>BRAÇO ARTICULADO</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>022-007356</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007356</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M12 x 30</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>6</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 933</t>
-        </is>
-      </c>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
@@ -3379,50 +4254,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>03.022-007319</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M8 x 30</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>8</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 933</t>
-        </is>
+          <t>MANCAL</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>022-007319</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007319</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>01.09.1.1.44.1.9</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M10 x 25</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>8</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 933</t>
-        </is>
-      </c>
+          <t>BARRA REDONDA 7" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="n">
+        <v>70</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>(mm) CONFERIR: desenho pede ASTM A36 Ø7"; no cadastro só existe Ø7" SAE 1020 (não há A36).</t>
         </is>
       </c>
     </row>
@@ -3435,50 +4336,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>03.022-007361</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M16 x 45</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>8</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 933</t>
-        </is>
+          <t>ANEL DE AJUSTE MAIOR</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>022-007361</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007361</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PARAF. CAB. SEXTAVADA M16 x 65</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>16</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 933</t>
-        </is>
-      </c>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
@@ -3491,50 +4418,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>03.022-007364</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NIPLE</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>10</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>AISI 304 1/4" NPT</t>
-        </is>
+          <t>ANEL DE AJUSTE DO EIXO</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>022-007364</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007364</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TAMPÃO Ø1" ROSCA BSP ANSI B16.3</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>2</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>ASTM A 197</t>
-        </is>
-      </c>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
@@ -3547,50 +4500,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>03.022-007360</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>UNIÃO ORIENTÁVEL SIMPLES</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>2</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>AISI 304 1/4" NPT</t>
-        </is>
+          <t>ANEL DE AJUSTE MENOR</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>022-007360</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>4</v>
+      </c>
+      <c r="H99" t="n">
+        <v>4</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007360</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DISTRIBUIDOR LINHA DUPLA BM-4</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>04 MÓDULOS/08 SAÍDAS EXIMPORT</t>
-        </is>
-      </c>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
     </row>
@@ -3603,50 +4582,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>03.022-007358</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ARRUELA LISA A-8,1</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>2</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>CL. 8.8 DIN 125</t>
-        </is>
+          <t>PINO MAIOR</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>022-007358</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007358</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>01.09.1.1.17.1.27</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PORCA SEXTAVADA M10</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>2</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Gr.8 DIN 934</t>
-        </is>
-      </c>
+          <t>BARRA REDONDA 1 3/4" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="n">
+        <v>160</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
@@ -3659,50 +4664,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>03.022-007363</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>TÊ ROSCA FÊMEA 6000Lbs</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>4</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>AISI 304 1/4" NPT</t>
-        </is>
+          <t>PINO MENOR DO BRAÇO</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>022-007363</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007363</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>01.09.1.1.15.1.27</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>TUBO Ø10 PAREDE 1MM X 6000MM</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>AISI 304</t>
-        </is>
-      </c>
+          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="n">
+        <v>100</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
@@ -3715,50 +4746,76 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>03.022-007359</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CONEXÃO JOELHO PARA TUBO 10MM</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>2</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>AISI 304 1/4" NPT</t>
-        </is>
+          <t>PINO MENOR</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>022-007359</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
-        </is>
-      </c>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007359</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>01.09.1.1.15.1.27</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PARAF.ALLEN C/CAB.SEXT. INTER. M6 x 55</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>2</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Gr. 8.8 DIN 912</t>
-        </is>
-      </c>
+          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="n">
+        <v>120</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
         </is>
       </c>
     </row>
@@ -3771,55 +4828,80 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>GAXETA QUAD. 2202 TEADIT</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>CARBONO + GRAFITE 1/4" x 1/4" x 900MM</t>
-        </is>
+          <t>TAMPÃO</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>022-007371</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>8</v>
+      </c>
+      <c r="H107" t="n">
+        <v>8</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Código Nomus a informar</t>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>01.09.1.1.1.1.9</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>JUNTA METALBEST (022-007370)</t>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>022-007370</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>2</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>INOX / GRAFITE</t>
-        </is>
-      </c>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="n">
+        <v>10</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Comprado — código Nomus a informar</t>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
         </is>
       </c>
     </row>
@@ -3832,14 +4914,2232 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>03.022-007325</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>TAMPA LATERAL</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>022-007325</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>03.022-007325</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>03.022-007320</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SUPORTE DO ATUADOR USINADO</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>022-007320</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>03.022-007320</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>03.022-007321</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SUPORTE DO ATUADOR SOLDADO</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>022-007321</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>3</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>03.022-007321</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>03.022-007324</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CHAPA DE CONTATO DA VÁLVULA</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>022-007324</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>03.022-007324</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>(kg bruto calculado) Espessura 3/4" (decisão).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>3</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>03.022-007321</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>03.022-007322</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>BASE DE LIGAÇÃO</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>022-007322</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>2</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>03.022-007322</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>3</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>03.022-007321</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>03.022-007323</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CHAPA DE CONTROLE DO ATUADOR</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>022-007323</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>03.022-007323</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>03.022-007347-REC</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CONJUNTO DISCO USINADO</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>022-007347</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Disco existente (REC) 022-007348.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>03.022-007347-REC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>03.022-007346-1</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CONJUNTO DISCO SOLDADO</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>022-007346</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>3</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>03.022-007346-1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>03.022-007349</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BASE DO DISCO</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>022-007349</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>03.022-007349</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>COMPRADOS / NORMALIZADOS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>01.05.1.103</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ROLAMENTO AUTOCOMPENSADOR DE ROLOS SKF 22312 E</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="n">
+        <v>2</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>01.03.7.2.2.1.14</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ANEL ELÁSTICO EXTERNO DIN 471 AÇO MOLA 60 mm</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Catálogo: DIN 471 aço mola 60 mm (desenho: SAE 1070).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>01.04.1.11.7.10</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>GAXETA QUADRADA TRANÇADA 3/8" FIOS DE CARBONO E GRAFITE FLEXÍVEL</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="n">
+        <v>10</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>CONFERIR: 3/8" fios de carbono e grafite flexível (cadastro em KG; desenho pede 3000 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>01.03.5.8.7.8.9.12</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>PINO ROSCADO DIN 976 AÇO CARBONO ZINCADO PRETO Ø12 X 60 mm</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="n">
+        <v>4</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Catálogo: DIN 976 Ø12 x 60 zincado preto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>01.03.3.1.2.69</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-13</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="n">
+        <v>10</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>1</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>01.03.2.1.4.2.7</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 CL. 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>4</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.15.19</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M30 - P.3,5 x 100</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>01.03.3.3.2.72</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ARRUELA PRESSÃO - DIN 127-A AÇO CARBONO ZINCADO PRETO A-31</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="n">
+        <v>2</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>01.03.2.1.4.8.15</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 CL. 8.8 AÇO CARBONO M30 - P.3,5</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro CL 8.8 sem zincagem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.9.9</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 50</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>01.03.2.1.9.2.9</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 Gr. 8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="n">
+        <v>17</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>01.04.3.2.1.12.316</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>O'RING VITON ISO 3601 70/75 SHORE A Ø641 x 10 mm</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>01.03.1.7.4.1.2.4.4</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>PARAFUSO ALLEN SEM CABEÇA DIN 913 CL 8.8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0 x 25</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="n">
+        <v>6</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>01.03.2.1.1.2.4</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="n">
+        <v>6</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro CL. 8 (não há Gr.8 M6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>01.03.2.1.9.2.6</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 Gr. 8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="n">
+        <v>8</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>01.03.1.7.4.6.2.6.7</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PARAFUSO ALLEN SEM CABEÇA DIN 913 . AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 40</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="n">
+        <v>2</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro sem classe 8.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>01.03.3.1.2.55</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-10.5</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="n">
+        <v>28</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.6.8</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 45</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="n">
+        <v>6</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.7.5</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75 x 30</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="n">
+        <v>6</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.5.5</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M8 - P.1,25 x 30</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="n">
+        <v>8</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.6.4</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 25</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="n">
+        <v>8</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.9.8</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 45</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="n">
+        <v>8</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.9.12</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 65</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="n">
+        <v>16</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>01.13.3.349</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NIPLE INOX 304 – 1/4" NPT</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="n">
+        <v>10</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>CONFERIR: há também 01.13.3.18 (classe #150).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>1</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>01.13.3.14</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>TAMPÃO ASTM A 197 1" NPT - ANSI B16.3</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro é 1" NPT ASTM A197; desenho diz rosca BSP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>1</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>01.13.3.10</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>UNIÃO ORIENTÁVEL SIMPLES TUBO AISI 304 - 10 mm X 1/4" - NPT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>1</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>01.13.3.125</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDOR DE GRAXA BM4 – 4 MÓDULOS / 8 SAÍDAS EXIMPORT</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>01.03.3.1.2.71</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-8,1</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>01.03.2.1.9.2.6</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 Gr. 8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>01.13.2.6.1</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>TÊ FÊMEA 1/4" NPT AISI 304</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="n">
+        <v>4</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>01.13.1.13.2.10</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>TUBO 10 mm AISI 304 PD 1,0 mm</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>CONFERIR: há também 01.13.1.13.10.10. Qtd em mm (6000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>01.13.3.17</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CONEXÃO JOELHO TUBO 10 mm X 1/4" NPT INOX AISI 304</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="n">
+        <v>2</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>1</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>01.03.1.14.3.1.2.4.10</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>PARAFUSO ALLEN CABEÇA CILÍNDRICA SEXTAVADO INTERNO DIN 912 CL 8.8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0 x 55</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>01.04.1.11.3.39</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>GAXETA QUADRADA TRANÇADA 1/4" CARBONO COM GRAFITE FLEXÍVEL</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>CONFERIR: 1/4" carbono com grafite flexível (cadastro em KG; desenho pede 900 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>1</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>01.13.3.493</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>JUNTA METALBEST TIPO 927 INOX / GRAFITE Ø200 x Ø175 x 3,0 mm</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
           <t>PENDENTE: balões 52, 62, 65 sem linha na lista do desenho</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
         <is>
           <t>Definir descrição, material e qtd</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>1</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PENDENTE: desenho 022-007345 (barra superior da alavanca) sem desenho</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>022-007345</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Material/matéria-prima a definir</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Código sugerido</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>03.022-007319</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MANCAL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01.09.1.1.44.1.9</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CONFERIR: desenho pede ASTM A36 Ø7"; no cadastro só existe Ø7" SAE 1020 (não há A36).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GAXETA QUAD. 2202 TEADIT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>01.04.1.11.7.10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CONFERIR: 3/8" fios de carbono e grafite flexível (cadastro em KG; desenho pede 3000 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA M30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01.03.2.1.4.8.15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro CL 8.8 sem zincagem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA M6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>01.03.2.1.1.2.4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro CL. 8 (não há Gr.8 M6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PARAF.ALLEN S/ CAB. SEXT. INTERNO M10 x 40</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>01.03.1.7.4.6.2.6.7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro sem classe 8.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NIPLE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>01.13.3.349</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CONFERIR: há também 01.13.3.18 (classe #150).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TAMPÃO Ø1" ROSCA BSP ANSI B16.3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>01.13.3.14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro é 1" NPT ASTM A197; desenho diz rosca BSP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TUBO Ø10 PAREDE 1MM X 6000MM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>01.13.1.13.2.10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CONFERIR: há também 01.13.1.13.10.10. Qtd em mm (6000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GAXETA QUAD. 2202 TEADIT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01.04.1.11.3.39</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CONFERIR: 1/4" carbono com grafite flexível (cadastro em KG; desenho pede 900 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Balões 52/62/65</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Definir descrição, material e qtd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>03.022-007341</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Barra superior da alavanca 007345</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sem desenho — matéria-prima não definida</t>
         </is>
       </c>
     </row>

--- a/Estrutura_04.01.3.000598.xlsx
+++ b/Estrutura_04.01.3.000598.xlsx
@@ -7,10 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estrutura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A conferir" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importação" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estrutura" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A conferir" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Importação'!$A$1:$G$160</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -34,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +47,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,12 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,6 +440,5236 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G160"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Código pai</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Código do componente</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Qtd</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Un</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>03.022-007303-REC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CORPO USINADO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Corpo existente (REC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>03.022-007303-REC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>03.022-007302-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CORPO SOLDADO</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03.022-007302-1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>03.022-007307</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TUBO</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>03.022-007307</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01.13.1.57.14.24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TUBO Ø175 x Ø150 ASTM A516 Gr 70 .</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>125</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>03.022-007302-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>03.022-007308</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FLANGE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>03.022-007308</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>03.022-007302-1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>03.022-007304</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BOSSE 1</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>03.022-007304</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01.09.1.1.36.1.78</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 5" AÇO CARBONO ASTM A516 Gr.70</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>125</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>03.022-007302-1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>03.022-007305</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BOSSE 2</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>03.022-007305</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01.09.1.1.12.1.78</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 1/4" AÇO CARBONO ASTM A516 Gr.70</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>55</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>03.022-007302-1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>03.022-007312</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CONJUNTO SUPORTE USINADO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>03.022-007312</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>03.022-007309</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CONJUNTO SUPORTE SOLDADO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>03.022-007309</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>03.022-007310</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CHAPA INFERIOR</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>03.022-007310</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>03.022-007309</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>03.022-007311</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CHAPA LATERAL</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>03.022-007311</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 3/4"</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>03.022-007302-1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>03.022-007306</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CONJUNTO CAVALETE SOLDADO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>03.022-007306</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>03.022-007313</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PLACA DO CAVALETE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03.022-007313</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.52</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1"</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>03.022-007306</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>03.022-007314</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CHAPA 1</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>03.022-007314</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>03.022-007306</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>03.022-007315</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CHAPA 2</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>03.022-007315</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>03.022-007306</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>03.022-007316</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NERVURA 1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>03.022-007316</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>03.022-007306</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>03.022-007317</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NERVURA 2</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>03.022-007317</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>03.022-007355</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SUPORTE DO DISTRIBUIDOR</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>03.022-007355</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/8"</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>03.022-007326</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ANEL GUARDA PÓ</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>03.022-007326</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>03.022-007328</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ANEL LANTERNA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>03.022-007328</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>01.09.1.1.30.3.1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>03.022-007327</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ANEL ANTI EXTRUSÃO</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>03.022-007327</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>01.09.1.1.30.3.1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>15</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>03.022-007368</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CONJUNTO JANELA DE VISITA USINADA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>03.022-007368</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>03.022-007369</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CONJUNTO JANELA DE VISITA SOLDADA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>03.022-007369</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>03.022-007365</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FLANGE DA TAMPA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>03.022-007365</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>03.022-007369</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>03.022-007367</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TUBO DA TAMPA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>03.022-007367</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>01.13.1.5.4.4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TUBO 1" ASTM A36 SCH 80</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>50</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>03.022-007369</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>03.022-007366</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NERVURA DA TAMPA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>03.022-007366</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.11</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/2"</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>03.022-007329</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PREME GAXETA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>03.022-007329</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>03.022-007330</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PRENSA GAXETA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>03.022-007330</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>03.022-007334</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CHAVETA CENTRAL</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>03.022-007334</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>01.09.1.10.224.1.22</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BARRA CHAVETA 17 x 25 AÇO CARBONO SAE 1045</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>155</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>03.022-007318</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EIXO PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>03.022-007318</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>01.09.1.1.27.3.7</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 3" AÇO INOX AISI 420</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>03.022-007333</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CONJUNTO PLACA CENTRAL USINADO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>03.022-007333</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>03.022-007331</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PLACA CENTRAL SOLDADA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>03.022-007331</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>03.022-007340</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PLACA CENTRAL</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>03.022-007340</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>03.022-007331</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>03.022-007332</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BUCHA DA PLACA CENTRAL</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>03.022-007332</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>01.13.1.58.12.24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>38</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>03.022-007331</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TAMPÃO</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>01.09.1.1.1.1.9</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>03.022-007331</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>03.022-007336</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BUCHA CENTRAL 2</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>03.022-007336</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>01.13.1.59.12.24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TUBO Ø110 x Ø90 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>30</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>03.022-007335</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BUCHA CENTRAL</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>03.022-007335</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>01.13.1.60.12.24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TUBO Ø105 x Ø60 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>35</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>03.022-007342</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CONJUNTO ALAVANCA USINADA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>03.022-007342</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>03.022-007341</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CONJUNTO ALAVANCA SOLDADA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>03.022-007341</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>03.022-007344</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TUBO DA ALAVANCA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>03.022-007344</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>01.13.1.61.1.24</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TUBO Ø4" x Ø60 ASTM A106 GR C .</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>90</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>03.022-007341</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>03.022-007343</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CHAPA DA ALAVANCA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>03.022-007343</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>03.022-007341</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>03.022-007345</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BARRA SUPERIOR DA ALAVANCA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>03.022-007345</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>[DEFINIR] Matéria-prima da barra superior da alavanca (sem desenho 022-007345)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Sem desenho no PDF; peça espelhada da barra inferior (007350, chapa 1/2" A516 Gr70)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>03.022-007341</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>03.022-007350</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BARRA INFERIOR DA ALAVANCA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>03.022-007350</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>03.022-007351</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BUCHA DO CONJUNTO ALAVANCA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>03.022-007351</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>01.13.1.62.12.24</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TUBO Ø35 x Ø55 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>20</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>03.022-007352</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CONJUNTO SUPORTE DO DISCO USINADO</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>03.022-007352</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CONJUNTO SUPORTE DO DISCO SOLDADO</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>03.022-007338</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BASE DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>03.022-007338</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>03.022-007339</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CHAPA DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>03.022-007339</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>03.022-007353</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BUCHA MAIOR DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>03.022-007353</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>01.13.1.63.12.24</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TUBO Ø60 x Ø30 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>25</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>03.022-007354</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BUCHA MENOR DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>03.022-007354</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>01.13.1.58.12.24</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>25</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>03.022-007337</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TAMPÃO</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>01.09.1.1.1.1.9</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>03.022-007357</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BUCHA DO BRAÇO ARTICULADO</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>03.022-007357</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>01.13.1.58.12.24</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>20</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>03.022-007356</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BRAÇO ARTICULADO</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>03.022-007356</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>03.022-007319</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MANCAL</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>03.022-007319</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>01.09.1.1.44.1.9</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 7" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>70</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>(mm) CONFERIR: desenho pede ASTM A36 Ø7"; no cadastro só existe Ø7" SAE 1020 (não há A36).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>03.022-007361</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ANEL DE AJUSTE MAIOR</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>03.022-007361</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>03.022-007364</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ANEL DE AJUSTE DO EIXO</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>2</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>03.022-007364</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>03.022-007360</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ANEL DE AJUSTE MENOR</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>03.022-007360</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>03.022-007358</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PINO MAIOR</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>03.022-007358</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>01.09.1.1.17.1.27</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 3/4" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>160</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>03.022-007363</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PINO MENOR DO BRAÇO</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>03.022-007363</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>01.09.1.1.15.1.27</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>100</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>03.022-007359</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PINO MENOR</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>03.022-007359</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>01.09.1.1.15.1.27</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>120</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(mm) </t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>TAMPÃO</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>01.09.1.1.1.1.9</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>03.022-007325</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>TAMPA LATERAL</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>03.022-007325</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>03.022-007320</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SUPORTE DO ATUADOR USINADO</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>03.022-007320</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>03.022-007321</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SUPORTE DO ATUADOR SOLDADO</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>03.022-007321</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>03.022-007324</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CHAPA DE CONTATO DA VÁLVULA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>03.022-007324</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>(kg bruto calculado) Espessura 3/4" (decisão).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>03.022-007321</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>03.022-007322</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BASE DE LIGAÇÃO</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>03.022-007322</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>03.022-007321</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>03.022-007323</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CHAPA DE CONTROLE DO ATUADOR</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>03.022-007323</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>03.022-007347-REC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CONJUNTO DISCO USINADO</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Disco existente (REC) 022-007348.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>03.022-007347-REC</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>03.022-007346-1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>CONJUNTO DISCO SOLDADO</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>03.022-007346-1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>03.022-007349</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BASE DO DISCO</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Fabricado</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>03.022-007349</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(kg bruto calculado) </t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>01.05.1.103</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ROLAMENTO AUTOCOMPENSADOR DE ROLOS SKF 22312 E</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>01.03.7.2.2.1.14</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ANEL ELÁSTICO EXTERNO DIN 471 AÇO MOLA 60 mm</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Catálogo: DIN 471 aço mola 60 mm (desenho: SAE 1070).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>01.04.1.11.7.10</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>GAXETA QUADRADA TRANÇADA 3/8" FIOS DE CARBONO E GRAFITE FLEXÍVEL</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>CONFERIR: 3/8" fios de carbono e grafite flexível (cadastro em KG; desenho pede 3000 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>01.03.5.8.7.8.9.12</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PINO ROSCADO DIN 976 AÇO CARBONO ZINCADO PRETO Ø12 X 60 mm</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Catálogo: DIN 976 Ø12 x 60 zincado preto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>01.03.3.1.2.69</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-13</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>01.03.2.1.4.2.7</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 CL. 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.15.19</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M30 - P.3,5 x 100</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>01.03.3.3.2.72</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ARRUELA PRESSÃO - DIN 127-A AÇO CARBONO ZINCADO PRETO A-31</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>01.03.2.1.4.8.15</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 CL. 8.8 AÇO CARBONO M30 - P.3,5</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro CL 8.8 sem zincagem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.9.9</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 50</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>01.03.2.1.9.2.9</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 Gr. 8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>17</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>01.04.3.2.1.12.316</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>O'RING VITON ISO 3601 70/75 SHORE A Ø641 x 10 mm</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>01.03.1.7.4.1.2.4.4</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PARAFUSO ALLEN SEM CABEÇA DIN 913 CL 8.8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0 x 25</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>6</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>01.03.2.1.1.2.4</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>6</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro CL. 8 (não há Gr.8 M6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>01.03.2.1.9.2.6</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 Gr. 8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>8</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>01.03.1.7.4.6.2.6.7</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PARAFUSO ALLEN SEM CABEÇA DIN 913 . AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 40</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>2</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro sem classe 8.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>01.03.3.1.2.55</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-10.5</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>28</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.6.8</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 45</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>6</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.7.5</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75 x 30</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>6</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.5.5</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M8 - P.1,25 x 30</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>8</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.6.4</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 25</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>8</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.9.8</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 45</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>01.03.1.1.1.1.2.9.12</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 65</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>16</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>01.13.3.349</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NIPLE INOX 304 – 1/4" NPT</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>CONFERIR: há também 01.13.3.18 (classe #150).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>01.13.3.14</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TAMPÃO ASTM A 197 1" NPT - ANSI B16.3</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>2</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>CONFERIR: cadastro é 1" NPT ASTM A197; desenho diz rosca BSP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>01.13.3.10</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>UNIÃO ORIENTÁVEL SIMPLES TUBO AISI 304 - 10 mm X 1/4" - NPT</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>01.13.3.125</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDOR DE GRAXA BM4 – 4 MÓDULOS / 8 SAÍDAS EXIMPORT</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>01.03.3.1.2.71</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-8,1</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>01.03.2.1.9.2.6</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>PORCA SEXTAVADA - DIN 934 Gr. 8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>01.13.2.6.1</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>TÊ FÊMEA 1/4" NPT AISI 304</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>01.13.1.13.2.10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>TUBO 10 mm AISI 304 PD 1,0 mm</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>CONFERIR: há também 01.13.1.13.10.10. Qtd em mm (6000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>01.13.3.17</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CONEXÃO JOELHO TUBO 10 mm X 1/4" NPT INOX AISI 304</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>01.03.1.14.3.1.2.4.10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PARAFUSO ALLEN CABEÇA CILÍNDRICA SEXTAVADO INTERNO DIN 912 CL 8.8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0 x 55</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>01.04.1.11.3.39</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>GAXETA QUADRADA TRANÇADA 1/4" CARBONO COM GRAFITE FLEXÍVEL</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>CONFERIR: 1/4" carbono com grafite flexível (cadastro em KG; desenho pede 900 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>01.13.3.493</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>JUNTA METALBEST TIPO 927 INOX / GRAFITE Ø200 x Ø175 x 3,0 mm</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr"/>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>[DEFINIR] Item do balão 52 (aparece no desenho 022-007300, sem linha na lista)</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>Sem descrição na lista do desenho</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr"/>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>[DEFINIR] Item do balão 62 (aparece no desenho 022-007300, sem linha na lista)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr"/>
+      <c r="E159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>Sem descrição na lista do desenho</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr"/>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>[DEFINIR] Item do balão 65 (aparece no desenho 022-007300, sem linha na lista)</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr"/>
+      <c r="E160" s="4" t="inlineStr"/>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>Sem descrição na lista do desenho</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G160"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -527,7 +5767,6 @@
           <t>Produto acabado</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -615,7 +5854,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -657,7 +5895,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -683,11 +5920,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>125</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -739,7 +5974,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -765,11 +5999,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>6.2</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -821,7 +6053,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -847,11 +6078,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>125</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -903,7 +6132,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -929,11 +6157,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>55</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -985,7 +6211,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1027,7 +6252,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1069,7 +6293,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1095,11 +6318,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>1.05</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1151,7 +6372,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1177,11 +6397,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>1.88</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1233,7 +6451,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1275,7 +6492,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1301,11 +6517,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>12.46</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1357,7 +6571,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1383,11 +6596,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>3.07</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1439,7 +6650,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1465,11 +6675,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>5.88</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1521,7 +6729,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1547,11 +6754,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>0.59</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1603,7 +6808,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1629,11 +6833,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>1.54</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1685,7 +6887,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1711,11 +6912,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>0.86</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1767,7 +6966,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1793,11 +6991,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>1.09</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1849,7 +7045,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1875,11 +7070,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>20</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -1931,7 +7124,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1957,11 +7149,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>15</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2013,7 +7203,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2055,7 +7244,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2097,7 +7285,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2123,11 +7310,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>15.08</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2179,7 +7364,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2205,11 +7389,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>50</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2261,7 +7443,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2287,11 +7468,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
         <v>0.59</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2343,7 +7522,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2369,11 +7547,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>0.5</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2425,7 +7601,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2451,11 +7626,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
         <v>1.72</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2507,7 +7680,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2533,11 +7705,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>155</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2589,7 +7759,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2615,11 +7784,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>1250</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2671,7 +7838,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2713,7 +7879,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2755,7 +7920,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2781,11 +7945,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
         <v>11.95</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2837,7 +7999,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2863,11 +8024,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
         <v>38</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -2949,11 +8108,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>10</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3005,7 +8162,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3031,11 +8187,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
         <v>30</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3087,7 +8241,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3113,11 +8266,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>35</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3169,7 +8320,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3211,7 +8361,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3253,7 +8402,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3279,11 +8427,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>90</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3335,7 +8481,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3361,11 +8506,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>1.85</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3417,7 +8560,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3459,7 +8601,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3485,11 +8626,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
         <v>0.27</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3541,7 +8680,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3567,11 +8705,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
         <v>20</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3623,7 +8759,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3665,7 +8800,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3707,7 +8841,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3733,11 +8866,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
         <v>2.83</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3789,7 +8920,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3815,11 +8945,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>3.26</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3871,7 +8999,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3897,11 +9024,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>25</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -3953,7 +9078,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3979,11 +9103,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>25</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4065,11 +9187,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
         <v>10</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4121,7 +9241,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4147,11 +9266,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>20</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4203,7 +9320,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4229,11 +9345,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>1.86</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4285,7 +9399,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4311,11 +9424,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
         <v>70</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4367,7 +9478,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4393,11 +9503,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>0.28</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4449,7 +9557,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4475,11 +9582,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>1.89</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4531,7 +9636,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4557,11 +9661,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>0.2</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4613,7 +9715,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4639,11 +9740,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>160</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4695,7 +9794,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4721,11 +9819,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>100</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4777,7 +9873,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4803,11 +9898,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
         <v>120</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4889,11 +9982,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
         <v>10</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -4945,7 +10036,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4971,11 +10061,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
         <v>4.27</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -5027,7 +10115,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5069,7 +10156,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5111,7 +10197,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5137,11 +10222,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
         <v>9.35</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -5193,7 +10276,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5219,11 +10301,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
         <v>2.38</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -5275,7 +10355,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5301,11 +10380,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
         <v>9.35</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -5403,7 +10480,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5445,7 +10521,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5471,11 +10546,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
         <v>4.27</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
@@ -5487,21 +10560,13 @@
         </is>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>COMPRADOS / NORMALIZADOS</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5527,17 +10592,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
         <v>2</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5563,11 +10625,9 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
         <v>2</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -5603,11 +10663,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
         <v>10</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -5643,11 +10701,9 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
         <v>4</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -5683,17 +10739,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
         <v>10</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5719,17 +10772,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
         <v>4</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5755,17 +10805,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
         <v>1</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5791,17 +10838,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
         <v>2</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5827,11 +10871,9 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
         <v>1</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -5867,17 +10909,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
         <v>1</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5903,17 +10942,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
         <v>17</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -5939,17 +10975,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
         <v>1</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5975,17 +11008,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
         <v>6</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6011,11 +11041,9 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
         <v>6</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -6051,17 +11079,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
         <v>8</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6087,11 +11112,9 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
         <v>2</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -6127,17 +11150,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
         <v>28</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6163,17 +11183,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
         <v>6</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6199,17 +11216,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
         <v>6</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6235,17 +11249,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
         <v>8</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6271,17 +11282,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
         <v>8</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6307,17 +11315,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
         <v>8</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6343,17 +11348,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
         <v>16</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6379,11 +11381,9 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
         <v>10</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -6419,11 +11419,9 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
         <v>2</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -6459,17 +11457,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
         <v>2</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6495,17 +11490,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
         <v>1</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6531,17 +11523,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
         <v>2</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -6567,17 +11556,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
         <v>2</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -6603,17 +11589,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
         <v>4</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6639,11 +11622,9 @@
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
         <v>1</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -6679,17 +11660,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
         <v>2</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6715,17 +11693,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
         <v>2</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -6751,11 +11726,9 @@
           <t>QUILOGRAMA</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
         <v>1</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Comprado</t>
@@ -6791,17 +11764,14 @@
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
         <v>2</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6812,16 +11782,11 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>PENDENTE: balões 52, 62, 65 sem linha na lista do desenho</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -6842,20 +11807,16 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>PENDENTE: desenho 022-007345 (barra superior da alavanca) sem desenho</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>022-007345</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -6872,7 +11833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7118,7 +12079,6 @@
           <t>Balões 52/62/65</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>Definir descrição, material e qtd</t>
@@ -7136,7 +12096,6 @@
           <t>Barra superior da alavanca 007345</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Sem desenho — matéria-prima não definida</t>

--- a/Estrutura_04.01.3.000598.xlsx
+++ b/Estrutura_04.01.3.000598.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A conferir" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Importação'!$A$1:$G$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Importação'!$A$1:$K$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,50 +440,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Código pai</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Código do componente</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Qtd</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Un</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Matéria-prima (código)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Matéria-prima (descrição)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Qtd matéria-prima</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Un MP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
@@ -518,7 +542,11 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Corpo existente (REC).</t>
         </is>
@@ -554,6 +582,9 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -584,7 +615,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01.13.1.57.14.24</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TUBO Ø175 x Ø150 ASTM A516 Gr 70 .</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>125</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -617,6 +665,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>01.13.1.57.14.24</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TUBO Ø175 x Ø150 ASTM A516 Gr 70 .</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>125</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -650,7 +716,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -683,6 +766,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -716,7 +817,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>01.09.1.1.36.1.78</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 5" AÇO CARBONO ASTM A516 Gr.70</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>125</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -749,6 +867,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>01.09.1.1.36.1.78</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 5" AÇO CARBONO ASTM A516 Gr.70</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>125</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -782,7 +918,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>01.09.1.1.12.1.78</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 1/4" AÇO CARBONO ASTM A516 Gr.70</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>55</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -815,6 +968,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>01.09.1.1.12.1.78</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 1/4" AÇO CARBONO ASTM A516 Gr.70</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>55</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -849,6 +1020,9 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -880,6 +1054,9 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -910,7 +1087,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -943,6 +1137,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -976,7 +1188,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.4</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 3/4"</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1009,6 +1238,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.4</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 3/4"</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1043,6 +1290,9 @@
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1073,7 +1323,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1"</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1106,6 +1373,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1"</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1139,7 +1424,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1172,6 +1474,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1205,7 +1525,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1238,6 +1575,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1271,7 +1626,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1304,6 +1676,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1337,7 +1727,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1370,6 +1777,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1403,7 +1828,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.19</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/8"</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1436,6 +1878,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.19</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/8"</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1469,7 +1929,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1502,6 +1979,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1535,7 +2030,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>01.09.1.1.30.3.1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>20</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1568,6 +2080,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>01.09.1.1.30.3.1</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -1601,7 +2131,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>01.09.1.1.30.3.1</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1634,6 +2181,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>01.09.1.1.30.3.1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -1668,6 +2233,9 @@
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1699,6 +2267,9 @@
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1729,7 +2300,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1762,6 +2350,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1795,7 +2401,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>01.13.1.5.4.4</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>TUBO 1" ASTM A36 SCH 80</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>50</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1828,6 +2451,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>01.13.1.5.4.4</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TUBO 1" ASTM A36 SCH 80</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>50</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -1861,7 +2502,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.11</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/2"</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1894,6 +2552,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.11</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/2"</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1927,7 +2603,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1960,6 +2653,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -1993,7 +2704,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2026,6 +2754,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -2059,7 +2805,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>01.09.1.10.224.1.22</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>BARRA CHAVETA 17 x 25 AÇO CARBONO SAE 1045</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>155</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2092,6 +2855,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>01.09.1.10.224.1.22</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>BARRA CHAVETA 17 x 25 AÇO CARBONO SAE 1045</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>155</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -2125,7 +2906,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>01.09.1.1.27.3.7</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 3" AÇO INOX AISI 420</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1250</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2158,6 +2956,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>01.09.1.1.27.3.7</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 3" AÇO INOX AISI 420</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1250</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -2192,6 +3008,9 @@
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2223,6 +3042,9 @@
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2253,7 +3075,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2286,6 +3125,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -2319,7 +3176,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>01.13.1.58.12.24</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>38</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2352,6 +3226,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>01.13.1.58.12.24</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>38</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -2387,6 +3279,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>01.09.1.1.1.1.9</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>10</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
         </is>
       </c>
@@ -2422,6 +3332,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>01.09.1.1.1.1.9</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
         </is>
       </c>
@@ -2455,7 +3383,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>01.13.1.59.12.24</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TUBO Ø110 x Ø90 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>30</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2488,6 +3433,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>01.13.1.59.12.24</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>TUBO Ø110 x Ø90 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>30</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -2521,7 +3484,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>01.13.1.60.12.24</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TUBO Ø105 x Ø60 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>35</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2554,6 +3534,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>01.13.1.60.12.24</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TUBO Ø105 x Ø60 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>35</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -2588,6 +3586,9 @@
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2619,6 +3620,9 @@
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2649,7 +3653,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>01.13.1.61.1.24</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>TUBO Ø4" x Ø60 ASTM A106 GR C .</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>90</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2682,6 +3703,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>01.13.1.61.1.24</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>TUBO Ø4" x Ø60 ASTM A106 GR C .</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>90</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -2715,7 +3754,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2748,6 +3804,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -2782,6 +3856,9 @@
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -2789,20 +3866,24 @@
           <t>03.022-007345</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr"/>
+      <c r="B72" s="4" t="n"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
           <t>[DEFINIR] Matéria-prima da barra superior da alavanca (sem desenho 022-007345)</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr"/>
-      <c r="E72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr">
         <is>
           <t>Sem desenho no PDF; peça espelhada da barra inferior (007350, chapa 1/2" A516 Gr70)?</t>
         </is>
@@ -2837,7 +3918,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2870,6 +3968,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -2903,7 +4019,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>01.13.1.62.12.24</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>TUBO Ø35 x Ø55 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2936,6 +4069,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>01.13.1.62.12.24</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>TUBO Ø35 x Ø55 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>20</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -2970,6 +4121,9 @@
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3001,6 +4155,9 @@
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3031,7 +4188,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3064,6 +4238,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -3097,7 +4289,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3130,6 +4339,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -3163,7 +4390,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>01.13.1.63.12.24</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>TUBO Ø60 x Ø30 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>25</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3196,6 +4440,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>01.13.1.63.12.24</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TUBO Ø60 x Ø30 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>25</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -3229,7 +4491,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>01.13.1.58.12.24</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>25</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3262,6 +4541,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>01.13.1.58.12.24</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>25</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -3297,6 +4594,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>01.09.1.1.1.1.9</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>10</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
         </is>
       </c>
@@ -3332,6 +4647,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
+          <t>01.09.1.1.1.1.9</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>10</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
         </is>
       </c>
@@ -3365,7 +4698,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>01.13.1.58.12.24</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>20</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3398,6 +4748,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
+          <t>01.13.1.58.12.24</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>20</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -3431,7 +4799,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3464,6 +4849,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -3497,7 +4900,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>01.09.1.1.44.1.9</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 7" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>70</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3530,6 +4950,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
+          <t>01.09.1.1.44.1.9</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 7" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>70</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t>(mm) CONFERIR: desenho pede ASTM A36 Ø7"; no cadastro só existe Ø7" SAE 1020 (não há A36).</t>
         </is>
       </c>
@@ -3563,7 +5001,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3596,6 +5051,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -3629,7 +5102,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3662,6 +5152,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.6</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -3695,7 +5203,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3728,6 +5253,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -3761,7 +5304,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>01.09.1.1.17.1.27</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 3/4" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>160</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3794,6 +5354,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
+          <t>01.09.1.1.17.1.27</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 3/4" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>160</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -3827,7 +5405,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>01.09.1.1.15.1.27</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>100</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3860,6 +5455,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
+          <t>01.09.1.1.15.1.27</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>100</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -3893,7 +5506,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>01.09.1.1.15.1.27</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>120</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3926,6 +5556,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
+          <t>01.09.1.1.15.1.27</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>120</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">(mm) </t>
         </is>
       </c>
@@ -3961,6 +5609,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
+          <t>01.09.1.1.1.1.9</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>10</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
         </is>
       </c>
@@ -3996,6 +5662,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
+          <t>01.09.1.1.1.1.9</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>10</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>MILIMETRO</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
         </is>
       </c>
@@ -4029,7 +5713,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4062,6 +5763,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -4096,6 +5815,9 @@
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4127,6 +5849,9 @@
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4157,7 +5882,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4190,6 +5932,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t>(kg bruto calculado) Espessura 3/4" (decisão).</t>
         </is>
       </c>
@@ -4223,7 +5983,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4256,6 +6033,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -4289,7 +6084,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4322,6 +6134,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.4</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -4355,7 +6185,11 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
         <is>
           <t>Disco existente (REC) 022-007348.</t>
         </is>
@@ -4391,6 +6225,9 @@
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4421,7 +6258,24 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4454,6 +6308,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.3</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>QUILOGRAMA</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
       </c>
@@ -4488,6 +6360,9 @@
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4518,7 +6393,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
         <is>
           <t>Catálogo: DIN 471 aço mola 60 mm (desenho: SAE 1070).</t>
         </is>
@@ -4553,7 +6432,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
         <is>
           <t>CONFERIR: 3/8" fios de carbono e grafite flexível (cadastro em KG; desenho pede 3000 mm).</t>
         </is>
@@ -4588,7 +6471,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
         <is>
           <t>Catálogo: DIN 976 Ø12 x 60 zincado preto.</t>
         </is>
@@ -4624,6 +6511,9 @@
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4655,6 +6545,9 @@
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4686,6 +6579,9 @@
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4717,6 +6613,9 @@
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4747,7 +6646,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
         <is>
           <t>CONFERIR: cadastro CL 8.8 sem zincagem.</t>
         </is>
@@ -4783,6 +6686,9 @@
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4814,6 +6720,9 @@
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4845,6 +6754,9 @@
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4876,6 +6788,9 @@
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4906,7 +6821,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
         <is>
           <t>CONFERIR: cadastro CL. 8 (não há Gr.8 M6).</t>
         </is>
@@ -4942,6 +6861,9 @@
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4972,7 +6894,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
         <is>
           <t>CONFERIR: cadastro sem classe 8.8.</t>
         </is>
@@ -5008,6 +6934,9 @@
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5039,6 +6968,9 @@
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5070,6 +7002,9 @@
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5101,6 +7036,9 @@
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5132,6 +7070,9 @@
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5163,6 +7104,9 @@
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5194,6 +7138,9 @@
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5224,7 +7171,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
         <is>
           <t>CONFERIR: há também 01.13.3.18 (classe #150).</t>
         </is>
@@ -5259,7 +7210,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
         <is>
           <t>CONFERIR: cadastro é 1" NPT ASTM A197; desenho diz rosca BSP.</t>
         </is>
@@ -5295,6 +7250,9 @@
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5326,6 +7284,9 @@
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5357,6 +7318,9 @@
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5388,6 +7352,9 @@
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5419,6 +7386,9 @@
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5449,7 +7419,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
         <is>
           <t>CONFERIR: há também 01.13.1.13.10.10. Qtd em mm (6000).</t>
         </is>
@@ -5485,6 +7459,9 @@
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5516,6 +7493,9 @@
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5546,7 +7526,11 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
         <is>
           <t>CONFERIR: 1/4" carbono com grafite flexível (cadastro em KG; desenho pede 900 mm).</t>
         </is>
@@ -5582,6 +7566,9 @@
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -5589,20 +7576,24 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="B158" s="4" t="inlineStr"/>
+      <c r="B158" s="4" t="n"/>
       <c r="C158" s="4" t="inlineStr">
         <is>
           <t>[DEFINIR] Item do balão 52 (aparece no desenho 022-007300, sem linha na lista)</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr"/>
-      <c r="E158" s="4" t="inlineStr"/>
+      <c r="D158" s="4" t="n"/>
+      <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="G158" s="4" t="inlineStr">
+      <c r="G158" s="4" t="inlineStr"/>
+      <c r="H158" s="4" t="inlineStr"/>
+      <c r="I158" s="4" t="inlineStr"/>
+      <c r="J158" s="4" t="inlineStr"/>
+      <c r="K158" s="4" t="inlineStr">
         <is>
           <t>Sem descrição na lista do desenho</t>
         </is>
@@ -5614,20 +7605,24 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr"/>
+      <c r="B159" s="4" t="n"/>
       <c r="C159" s="4" t="inlineStr">
         <is>
           <t>[DEFINIR] Item do balão 62 (aparece no desenho 022-007300, sem linha na lista)</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr"/>
-      <c r="E159" s="4" t="inlineStr"/>
+      <c r="D159" s="4" t="n"/>
+      <c r="E159" s="4" t="n"/>
       <c r="F159" s="4" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="G159" s="4" t="inlineStr">
+      <c r="G159" s="4" t="inlineStr"/>
+      <c r="H159" s="4" t="inlineStr"/>
+      <c r="I159" s="4" t="inlineStr"/>
+      <c r="J159" s="4" t="inlineStr"/>
+      <c r="K159" s="4" t="inlineStr">
         <is>
           <t>Sem descrição na lista do desenho</t>
         </is>
@@ -5639,27 +7634,31 @@
           <t>04.01.3.000598</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr"/>
+      <c r="B160" s="4" t="n"/>
       <c r="C160" s="4" t="inlineStr">
         <is>
           <t>[DEFINIR] Item do balão 65 (aparece no desenho 022-007300, sem linha na lista)</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr"/>
-      <c r="E160" s="4" t="inlineStr"/>
+      <c r="D160" s="4" t="n"/>
+      <c r="E160" s="4" t="n"/>
       <c r="F160" s="4" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="G160" s="4" t="inlineStr">
+      <c r="G160" s="4" t="inlineStr"/>
+      <c r="H160" s="4" t="inlineStr"/>
+      <c r="I160" s="4" t="inlineStr"/>
+      <c r="J160" s="4" t="inlineStr"/>
+      <c r="K160" s="4" t="inlineStr">
         <is>
           <t>Sem descrição na lista do desenho</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G160"/>
+  <autoFilter ref="A1:K160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10560,7 +12559,6 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="C124" s="2" t="inlineStr">
         <is>

--- a/Estrutura_04.01.3.000598.xlsx
+++ b/Estrutura_04.01.3.000598.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1DD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -67,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -75,6 +80,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,10 +455,10 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="70" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -489,22 +495,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Matéria-prima (código)</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Matéria-prima (descrição)</t>
+          <t>Espessura / bitola (mm)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Qtd matéria-prima</t>
+          <t>Dimensão bruta</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Un MP</t>
+          <t>Peso (kg)  [peça = acabado; MP = bruto]</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -542,10 +548,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>323.7</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Corpo existente (REC).</t>
@@ -581,10 +586,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>323.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -615,73 +619,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007307</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>01.13.1.57.14.24</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>TUBO Ø175 x Ø150 ASTM A516 Gr 70 .</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="D5" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>03.022-007307</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>01.13.1.57.14.24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TUBO Ø175 x Ø150 ASTM A516 Gr 70 .</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>125</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>01.13.1.57.14.24</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>TUBO Ø175 x Ø150 ASTM A516 Gr 70 .</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>125</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Ø175 x Ø150 x 125 mm</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -716,73 +703,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007308</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="D7" s="5" t="n">
         <v>6.2</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>03.022-007308</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>chapa 1"</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n">
         <v>6.2</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.6</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -817,73 +787,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007304</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.36.1.78</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 5" AÇO CARBONO ASTM A516 Gr.70</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="D9" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>03.022-007304</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>01.09.1.1.36.1.78</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 5" AÇO CARBONO ASTM A516 Gr.70</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>125</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>01.09.1.1.36.1.78</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 5" AÇO CARBONO ASTM A516 Gr.70</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>125</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Ø127.0 x 125 mm</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -918,73 +871,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007305</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.12.1.78</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 1 1/4" AÇO CARBONO ASTM A516 Gr.70</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="D11" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>03.022-007305</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01.09.1.1.12.1.78</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1 1/4" AÇO CARBONO ASTM A516 Gr.70</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>55</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>01.09.1.1.12.1.78</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1 1/4" AÇO CARBONO ASTM A516 Gr.70</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>55</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Ø31.8 x 55 mm</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -1019,10 +955,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1053,10 +988,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1087,73 +1021,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007310</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="D15" s="5" t="n">
         <v>1.05</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>03.022-007310</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1793.88</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 5/8"</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="n">
         <v>1.05</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -1188,73 +1105,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007311</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.4</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 3/4"</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="D17" s="5" t="n">
         <v>1.88</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>03.022-007311</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 3/4"</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1797.05</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 3/4"</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="n">
         <v>1.88</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.4</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 3/4"</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -1289,10 +1189,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>19.7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1323,73 +1222,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007313</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.52</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1"</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="D20" s="5" t="n">
         <v>12.46</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>03.022-007313</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.52</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1"</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>chapa 1"</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>12.46</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.52</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1"</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -1424,73 +1306,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007314</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="D22" s="5" t="n">
         <v>3.07</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>03.022-007314</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>chapa 5/8"</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>3.07</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -1525,73 +1390,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="J23" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007315</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="D24" s="5" t="n">
         <v>5.88</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>03.022-007315</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>chapa 5/8"</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>5.88</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -1626,73 +1474,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007316</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="D26" s="5" t="n">
         <v>0.59</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>03.022-007316</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>chapa 5/8"</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>0.59</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -1727,73 +1558,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="J27" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007317</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="D28" s="5" t="n">
         <v>1.54</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>03.022-007317</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>chapa 5/8"</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="n">
         <v>1.54</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -1828,73 +1642,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="J29" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007355</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.19</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/8"</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="D30" s="5" t="n">
         <v>0.86</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>03.022-007355</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.19</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/8"</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>chapa 1/8"</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>0.86</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.19</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/8"</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -1929,73 +1726,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="J31" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007326</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="D32" s="5" t="n">
         <v>1.09</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>03.022-007326</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>1790.7</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 1/2"</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n">
         <v>1.09</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -2030,73 +1810,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="J33" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007328</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.30.3.1</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="D34" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>03.022-007328</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>01.09.1.1.30.3.1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>20</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>01.09.1.1.30.3.1</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>20</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>AISI 304</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Ø88.9 x 20 mm</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -2131,73 +1894,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="J35" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007327</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.30.3.1</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="D36" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>03.022-007327</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>01.09.1.1.30.3.1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>15</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>01.09.1.1.30.3.1</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>AISI 304</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Ø88.9 x 15 mm</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -2232,10 +1978,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2266,10 +2011,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>10.7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2300,73 +2044,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="J39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007365</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="D40" s="5" t="n">
         <v>15.08</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>03.022-007365</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.6</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>chapa 1"</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="n">
         <v>15.08</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.6</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -2401,73 +2128,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="J41" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007367</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>01.13.1.5.4.4</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>TUBO 1" ASTM A36 SCH 80</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="D42" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>03.022-007367</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>01.13.1.5.4.4</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>TUBO 1" ASTM A36 SCH 80</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>50</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>01.13.1.5.4.4</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>TUBO 1" ASTM A36 SCH 80</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>50</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>1" SCH80 x 50 mm</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -2502,73 +2212,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="J43" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007366</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.11</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/2"</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="D44" s="5" t="n">
         <v>0.59</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>03.022-007366</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.11</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/2"</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>chapa 1/2"</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>0.59</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.11</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/2"</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -2603,73 +2296,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="J45" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007329</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.4</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="D46" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>03.022-007329</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.4</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>chapa 3/4"</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.4</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -2704,73 +2380,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="J47" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007330</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="D48" s="5" t="n">
         <v>1.72</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>03.022-007330</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>chapa 5/8"</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>1.72</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -2805,73 +2464,58 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="J49" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007334</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>01.09.1.10.224.1.22</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>BARRA CHAVETA 17 x 25 AÇO CARBONO SAE 1045</t>
         </is>
       </c>
-      <c r="I49" t="n">
+      <c r="D50" s="5" t="n">
         <v>155</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>03.022-007334</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>01.09.1.10.224.1.22</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>BARRA CHAVETA 17 x 25 AÇO CARBONO SAE 1045</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>155</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>01.09.1.10.224.1.22</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>BARRA CHAVETA 17 x 25 AÇO CARBONO SAE 1045</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>155</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>SAE 1045</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>17x25</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>17x25x155 mm</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -2906,73 +2550,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="J51" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007318</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.27.3.7</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 3" AÇO INOX AISI 420</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="D52" s="5" t="n">
         <v>1250</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>03.022-007318</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>01.09.1.1.27.3.7</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 3" AÇO INOX AISI 420</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>01.09.1.1.27.3.7</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 3" AÇO INOX AISI 420</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>1250</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>AISI 420</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Ø76.2 x 1250 mm</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>44.749</v>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -3007,10 +2634,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3041,10 +2667,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3075,73 +2700,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="J55" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007340</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="D56" s="5" t="n">
         <v>11.95</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>03.022-007340</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.6</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>chapa 1"</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="n">
         <v>11.95</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.6</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -3176,73 +2784,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="J57" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007332</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>01.13.1.58.12.24</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="D58" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>03.022-007332</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>01.13.1.58.12.24</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>38</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>01.13.1.58.12.24</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>38</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Ø50 x Ø27 x 38 mm</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -3277,78 +2868,61 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="J59" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.1.1.9</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
         </is>
       </c>
-      <c r="I59" t="n">
+      <c r="D60" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>03.022-007371</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>01.09.1.1.1.1.9</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>01.09.1.1.1.1.9</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>10</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>SAE 1020</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Ø6.3 x 10 mm</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
         </is>
@@ -3383,73 +2957,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="J61" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007336</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>01.13.1.59.12.24</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>TUBO Ø110 x Ø90 SAE 8550 .</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="D62" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>03.022-007336</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>01.13.1.59.12.24</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>TUBO Ø110 x Ø90 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>30</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>01.13.1.59.12.24</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>TUBO Ø110 x Ø90 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>30</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Ø110 x Ø90 x 30 mm</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -3484,73 +3041,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="J63" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007335</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>01.13.1.60.12.24</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>TUBO Ø105 x Ø60 SAE 8550 .</t>
         </is>
       </c>
-      <c r="I63" t="n">
+      <c r="D64" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>03.022-007335</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>01.13.1.60.12.24</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>TUBO Ø105 x Ø60 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>35</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>01.13.1.60.12.24</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>TUBO Ø105 x Ø60 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="I64" t="n">
-        <v>35</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Ø105 x Ø60 x 35 mm</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -3585,10 +3125,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3619,10 +3158,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3653,73 +3191,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="J67" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007344</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>01.13.1.61.1.24</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>TUBO Ø4" x Ø60 ASTM A106 GR C .</t>
         </is>
       </c>
-      <c r="I67" t="n">
+      <c r="D68" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>03.022-007344</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>01.13.1.61.1.24</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>TUBO Ø4" x Ø60 ASTM A106 GR C .</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>90</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>01.13.1.61.1.24</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>TUBO Ø4" x Ø60 ASTM A106 GR C .</t>
-        </is>
-      </c>
-      <c r="I68" t="n">
-        <v>90</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A106 GR C</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Ø101.6 x Ø60 x 90 mm</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -3754,73 +3275,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="J69" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007343</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
-      <c r="I69" t="n">
+      <c r="D70" s="5" t="n">
         <v>1.85</v>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>03.022-007343</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>1793.88</v>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 5/8"</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="n">
         <v>1.85</v>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
+      <c r="K70" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -3855,10 +3359,6 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -3918,73 +3418,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="J73" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007350</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
-      <c r="I73" t="n">
+      <c r="D74" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>03.022-007350</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>1790.7</v>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 1/2"</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -4019,73 +3502,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="J75" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007351</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>01.13.1.62.12.24</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>TUBO Ø35 x Ø55 SAE 8550 .</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="D76" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>03.022-007351</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>01.13.1.62.12.24</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>TUBO Ø35 x Ø55 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>20</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>01.13.1.62.12.24</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>TUBO Ø35 x Ø55 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>20</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Ø35 x Ø55 x 20 mm</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -4120,10 +3586,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4154,10 +3619,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4188,73 +3652,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="J79" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007338</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
-      <c r="I79" t="n">
+      <c r="D80" s="5" t="n">
         <v>2.83</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>03.022-007338</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>1790.7</v>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 1/2"</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="n">
         <v>2.83</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -4289,73 +3736,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="J81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007339</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
-      <c r="I81" t="n">
+      <c r="D82" s="5" t="n">
         <v>3.26</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>03.022-007339</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>1793.88</v>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 5/8"</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="n">
         <v>3.26</v>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -4390,73 +3820,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="J83" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007353</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>01.13.1.63.12.24</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>TUBO Ø60 x Ø30 SAE 8550 .</t>
         </is>
       </c>
-      <c r="I83" t="n">
+      <c r="D84" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>03.022-007353</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>01.13.1.63.12.24</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>TUBO Ø60 x Ø30 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>25</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>01.13.1.63.12.24</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>TUBO Ø60 x Ø30 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>25</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Ø60 x Ø30 x 25 mm</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -4491,73 +3904,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="J85" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007354</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>01.13.1.58.12.24</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
         </is>
       </c>
-      <c r="I85" t="n">
+      <c r="D86" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>03.022-007354</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>01.13.1.58.12.24</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>25</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>01.13.1.58.12.24</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>25</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Ø50 x Ø27 x 25 mm</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -4592,78 +3988,61 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="J87" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.1.1.9</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
         </is>
       </c>
-      <c r="I87" t="n">
+      <c r="D88" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>03.022-007371</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>01.09.1.1.1.1.9</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>01.09.1.1.1.1.9</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>10</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>SAE 1020</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Ø6.3 x 10 mm</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
         <is>
           <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
         </is>
@@ -4698,73 +4077,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="J89" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007357</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>01.13.1.58.12.24</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
         </is>
       </c>
-      <c r="I89" t="n">
+      <c r="D90" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>03.022-007357</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>01.13.1.58.12.24</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>20</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>01.13.1.58.12.24</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>TUBO Ø50 x Ø27 SAE 8550 .</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>20</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Ø50 x Ø27 x 20 mm</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -4799,73 +4161,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="J91" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007356</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
-      <c r="I91" t="n">
+      <c r="D92" s="5" t="n">
         <v>1.86</v>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>03.022-007356</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>1793.88</v>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 5/8"</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="n">
         <v>1.86</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
+      <c r="K92" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -4900,73 +4245,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="J93" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007319</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.44.1.9</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 7" AÇO CARBONO SAE 1020</t>
         </is>
       </c>
-      <c r="I93" t="n">
+      <c r="D94" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>03.022-007319</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>01.09.1.1.44.1.9</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 7" AÇO CARBONO SAE 1020</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>70</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>01.09.1.1.44.1.9</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 7" AÇO CARBONO SAE 1020</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>70</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>SAE 1020</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Ø177.8 x 70 mm</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>13.643</v>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
         <is>
           <t>(mm) CONFERIR: desenho pede ASTM A36 Ø7"; no cadastro só existe Ø7" SAE 1020 (não há A36).</t>
         </is>
@@ -5001,73 +4329,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="J95" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007361</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
-      <c r="I95" t="n">
+      <c r="D96" s="5" t="n">
         <v>0.28</v>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>03.022-007361</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>1790.7</v>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 1/2"</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="n">
         <v>0.28</v>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
+      <c r="K96" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -5102,73 +4413,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="J97" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007364</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
-      <c r="I97" t="n">
+      <c r="D98" s="5" t="n">
         <v>1.89</v>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>03.022-007364</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.6</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>chapa 1"</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="n">
         <v>1.89</v>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.6</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
+      <c r="K98" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -5203,73 +4497,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="J99" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007360</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
-      <c r="I99" t="n">
+      <c r="D100" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>03.022-007360</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>1790.7</v>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 1/2"</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.11</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
+      <c r="K100" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -5304,73 +4581,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="J101" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007358</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.17.1.27</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 1 3/4" AÇO CARBONO SAE 8550</t>
         </is>
       </c>
-      <c r="I101" t="n">
+      <c r="D102" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>03.022-007358</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>01.09.1.1.17.1.27</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1 3/4" AÇO CARBONO SAE 8550</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>160</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>01.09.1.1.17.1.27</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1 3/4" AÇO CARBONO SAE 8550</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>160</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Ø44.4 x 160 mm</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>1.949</v>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -5405,73 +4665,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="J103" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007363</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.15.1.27</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
         </is>
       </c>
-      <c r="I103" t="n">
+      <c r="D104" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="E104" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>03.022-007363</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>01.09.1.1.15.1.27</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>100</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>01.09.1.1.15.1.27</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>100</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Ø38.1 x 100 mm</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -5506,73 +4749,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="J105" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007359</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.15.1.27</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
         </is>
       </c>
-      <c r="I105" t="n">
+      <c r="D106" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="E106" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>03.022-007359</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>01.09.1.1.15.1.27</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>120</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>01.09.1.1.15.1.27</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>120</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>SAE 8550</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Ø38.1 x 120 mm</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(mm) </t>
         </is>
@@ -5607,78 +4833,61 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="J107" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007371</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>01.09.1.1.1.1.9</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
         </is>
       </c>
-      <c r="I107" t="n">
+      <c r="D108" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>MILIMETRO</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Matéria-prima Ø6 x 10 mm (sobremetal).</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>03.022-007371</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>01.09.1.1.1.1.9</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
         <is>
           <t>Matéria-prima</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>01.09.1.1.1.1.9</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>BARRA REDONDA 1/4" AÇO CARBONO SAE 1020</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
-        <v>10</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>MILIMETRO</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>SAE 1020</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Ø6.3 x 10 mm</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
         <is>
           <t>(mm) Ø6 x 10 mm (sobremetal de usinagem, decisão).</t>
         </is>
@@ -5713,73 +4922,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="J109" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007325</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
-      <c r="I109" t="n">
+      <c r="D110" s="5" t="n">
         <v>4.27</v>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="E110" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>03.022-007325</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>chapa 5/8"</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="n">
         <v>4.27</v>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
+      <c r="K110" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -5814,10 +5006,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="n">
+        <v>16.1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5848,10 +5039,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+      <c r="J112" t="n">
+        <v>16.1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5882,73 +5072,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="J113" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007324</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.4</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
         </is>
       </c>
-      <c r="I113" t="n">
+      <c r="D114" s="5" t="n">
         <v>9.35</v>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="E114" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>03.022-007324</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.4</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>chapa 3/4"</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="n">
         <v>9.35</v>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.4</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
-        </is>
-      </c>
-      <c r="I114" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
+      <c r="K114" s="5" t="inlineStr">
         <is>
           <t>(kg bruto calculado) Espessura 3/4" (decisão).</t>
         </is>
@@ -5983,73 +5156,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="J115" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007322</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
-      <c r="I115" t="n">
+      <c r="D116" s="5" t="n">
         <v>2.38</v>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>03.022-007322</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>chapa 5/8"</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="n">
         <v>2.38</v>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.3</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="I116" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
+      <c r="K116" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -6084,73 +5240,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="J117" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007323</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.1.5.4</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
         </is>
       </c>
-      <c r="I117" t="n">
+      <c r="D118" s="5" t="n">
         <v>9.35</v>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>03.022-007323</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.4</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A36</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>chapa 3/4"</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="n">
         <v>9.35</v>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.4</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
-        </is>
-      </c>
-      <c r="I118" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
+      <c r="K118" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -6185,10 +5324,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>72.8</v>
+      </c>
       <c r="K119" t="inlineStr">
         <is>
           <t>Disco existente (REC) 022-007348.</t>
@@ -6224,10 +5362,9 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+      <c r="J120" t="n">
+        <v>72.8</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6258,73 +5395,56 @@
           <t>Fabricado</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="J121" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>03.022-007349</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
-      <c r="I121" t="n">
+      <c r="D122" s="5" t="n">
         <v>4.27</v>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="E122" s="5" t="inlineStr">
         <is>
           <t>QUILOGRAMA</t>
         </is>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>03.022-007349</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Matéria-prima</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>ASTM A516 GR70</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>1793.88</v>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>chapa 70 5/8"</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="n">
         <v>4.27</v>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Matéria-prima</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>01.09.3.1.2.4.3</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>QUILOGRAMA</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
+      <c r="K122" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">(kg bruto calculado) </t>
         </is>
@@ -6359,10 +5479,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6393,10 +5509,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>Catálogo: DIN 471 aço mola 60 mm (desenho: SAE 1070).</t>
@@ -6432,10 +5544,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>CONFERIR: 3/8" fios de carbono e grafite flexível (cadastro em KG; desenho pede 3000 mm).</t>
@@ -6471,10 +5579,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>Catálogo: DIN 976 Ø12 x 60 zincado preto.</t>
@@ -6510,10 +5614,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6544,10 +5644,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6578,10 +5674,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6612,10 +5704,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6646,10 +5734,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>CONFERIR: cadastro CL 8.8 sem zincagem.</t>
@@ -6685,10 +5769,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6719,10 +5799,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6753,10 +5829,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6787,10 +5859,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6821,10 +5889,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>CONFERIR: cadastro CL. 8 (não há Gr.8 M6).</t>
@@ -6860,10 +5924,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6894,10 +5954,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>CONFERIR: cadastro sem classe 8.8.</t>
@@ -6933,10 +5989,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6967,10 +6019,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7001,10 +6049,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7035,10 +6079,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7069,10 +6109,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7103,10 +6139,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7137,10 +6169,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7171,10 +6199,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>CONFERIR: há também 01.13.3.18 (classe #150).</t>
@@ -7210,10 +6234,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>CONFERIR: cadastro é 1" NPT ASTM A197; desenho diz rosca BSP.</t>
@@ -7249,10 +6269,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7283,10 +6299,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7317,10 +6329,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7351,10 +6359,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7385,10 +6389,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7419,10 +6419,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>CONFERIR: há também 01.13.1.13.10.10. Qtd em mm (6000).</t>
@@ -7458,10 +6454,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7492,10 +6484,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7526,10 +6514,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>CONFERIR: 1/4" carbono com grafite flexível (cadastro em KG; desenho pede 900 mm).</t>
@@ -7565,10 +6549,6 @@
           <t>Comprado</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">

--- a/Estrutura_04.01.3.000598.xlsx
+++ b/Estrutura_04.01.3.000598.xlsx
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>1793.88</v>
+        <v>15.88</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 5/8"</t>
+          <t>chapa 5/8"</t>
         </is>
       </c>
       <c r="J15" s="5" t="n">
@@ -1144,11 +1144,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1797.05</v>
+        <v>19.05</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 3/4"</t>
+          <t>chapa 3/4"</t>
         </is>
       </c>
       <c r="J17" s="5" t="n">
@@ -1765,11 +1765,11 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1790.7</v>
+        <v>12.7</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 1/2"</t>
+          <t>chapa 1/2"</t>
         </is>
       </c>
       <c r="J32" s="5" t="n">
@@ -3314,11 +3314,11 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>1793.88</v>
+        <v>15.88</v>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 5/8"</t>
+          <t>chapa 5/8"</t>
         </is>
       </c>
       <c r="J70" s="5" t="n">
@@ -3457,11 +3457,11 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>1790.7</v>
+        <v>12.7</v>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 1/2"</t>
+          <t>chapa 1/2"</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
@@ -3691,11 +3691,11 @@
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>1790.7</v>
+        <v>12.7</v>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 1/2"</t>
+          <t>chapa 1/2"</t>
         </is>
       </c>
       <c r="J80" s="5" t="n">
@@ -3775,11 +3775,11 @@
         </is>
       </c>
       <c r="H82" s="5" t="n">
-        <v>1793.88</v>
+        <v>15.88</v>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 5/8"</t>
+          <t>chapa 5/8"</t>
         </is>
       </c>
       <c r="J82" s="5" t="n">
@@ -4200,11 +4200,11 @@
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>1793.88</v>
+        <v>15.88</v>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 5/8"</t>
+          <t>chapa 5/8"</t>
         </is>
       </c>
       <c r="J92" s="5" t="n">
@@ -4368,11 +4368,11 @@
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>1790.7</v>
+        <v>12.7</v>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 1/2"</t>
+          <t>chapa 1/2"</t>
         </is>
       </c>
       <c r="J96" s="5" t="n">
@@ -4536,11 +4536,11 @@
         </is>
       </c>
       <c r="H100" s="5" t="n">
-        <v>1790.7</v>
+        <v>12.7</v>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 1/2"</t>
+          <t>chapa 1/2"</t>
         </is>
       </c>
       <c r="J100" s="5" t="n">
@@ -5434,11 +5434,11 @@
         </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>1793.88</v>
+        <v>15.88</v>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>chapa 70 5/8"</t>
+          <t>chapa 5/8"</t>
         </is>
       </c>
       <c r="J122" s="5" t="n">
